--- a/Financial Analysis/AIR.xlsx
+++ b/Financial Analysis/AIR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6D4587-8D03-4269-9B68-9860A46D1F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CA008A-4896-4E21-88CC-313A9559C543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{07D530EB-ED3E-4FE7-ACCA-598769C814C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{07D530EB-ED3E-4FE7-ACCA-598769C814C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
   <si>
     <t>AIR</t>
   </si>
@@ -146,14 +146,45 @@
   </si>
   <si>
     <t>Net Margin</t>
+  </si>
+  <si>
+    <t>Maturity</t>
+  </si>
+  <si>
+    <t>Discount rate</t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+  <si>
+    <t>Net cash</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Per share</t>
+  </si>
+  <si>
+    <t>Current price</t>
+  </si>
+  <si>
+    <t>Variance</t>
+  </si>
+  <si>
+    <t>Consensus</t>
+  </si>
+  <si>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ [$€-484]"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ [$€-1]"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -228,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -243,6 +274,11 @@
     <xf numFmtId="4" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -258,6 +294,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02780903-9011-F309-528A-84BCFD1A90EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6934200" y="7620"/>
+          <a:ext cx="0" cy="7048500"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -591,7 +682,7 @@
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45771</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="5">
         <v>45777</v>
@@ -666,12 +757,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE816CCF-DE88-4637-A6DE-75C4B7BD6D1F}">
-  <dimension ref="B2:U34"/>
+  <dimension ref="B2:EE35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="23" width="8.88671875" style="1"/>
+    <col min="24" max="24" width="12.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="16.33203125" style="1" customWidth="1"/>
+    <col min="26" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.3">
@@ -749,6 +843,50 @@
       <c r="J3" s="8">
         <v>69230</v>
       </c>
+      <c r="K3" s="8">
+        <f>J3*1.04</f>
+        <v>71999.199999999997</v>
+      </c>
+      <c r="L3" s="8">
+        <f>K3*1.03</f>
+        <v>74159.175999999992</v>
+      </c>
+      <c r="M3" s="8">
+        <f>L3*1.02</f>
+        <v>75642.359519999998</v>
+      </c>
+      <c r="N3" s="8">
+        <f t="shared" ref="N3:U3" si="0">M3*1.02</f>
+        <v>77155.206710400002</v>
+      </c>
+      <c r="O3" s="8">
+        <f t="shared" si="0"/>
+        <v>78698.310844608</v>
+      </c>
+      <c r="P3" s="8">
+        <f t="shared" si="0"/>
+        <v>80272.277061500165</v>
+      </c>
+      <c r="Q3" s="8">
+        <f t="shared" si="0"/>
+        <v>81877.722602730166</v>
+      </c>
+      <c r="R3" s="8">
+        <f t="shared" si="0"/>
+        <v>83515.277054784776</v>
+      </c>
+      <c r="S3" s="8">
+        <f t="shared" si="0"/>
+        <v>85185.582595880478</v>
+      </c>
+      <c r="T3" s="8">
+        <f t="shared" si="0"/>
+        <v>86889.294247798083</v>
+      </c>
+      <c r="U3" s="8">
+        <f t="shared" si="0"/>
+        <v>88627.080132754039</v>
+      </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -772,34 +910,122 @@
       <c r="J4" s="6">
         <v>58555</v>
       </c>
+      <c r="K4" s="6">
+        <f>K3-K5</f>
+        <v>59759.335999999996</v>
+      </c>
+      <c r="L4" s="6">
+        <f t="shared" ref="L4:U4" si="1">L3-L5</f>
+        <v>61552.116079999993</v>
+      </c>
+      <c r="M4" s="6">
+        <f t="shared" si="1"/>
+        <v>62783.158401599998</v>
+      </c>
+      <c r="N4" s="6">
+        <f t="shared" si="1"/>
+        <v>64038.821569631997</v>
+      </c>
+      <c r="O4" s="6">
+        <f t="shared" si="1"/>
+        <v>65319.598001024642</v>
+      </c>
+      <c r="P4" s="6">
+        <f t="shared" si="1"/>
+        <v>66625.989961045139</v>
+      </c>
+      <c r="Q4" s="6">
+        <f t="shared" si="1"/>
+        <v>67958.509760266039</v>
+      </c>
+      <c r="R4" s="6">
+        <f t="shared" si="1"/>
+        <v>69317.679955471365</v>
+      </c>
+      <c r="S4" s="6">
+        <f t="shared" si="1"/>
+        <v>70704.03355458079</v>
+      </c>
+      <c r="T4" s="6">
+        <f t="shared" si="1"/>
+        <v>72118.114225672412</v>
+      </c>
+      <c r="U4" s="6">
+        <f t="shared" si="1"/>
+        <v>73560.47651018585</v>
+      </c>
     </row>
     <row r="5" spans="2:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="8">
-        <f>E3-E4</f>
+        <f t="shared" ref="E5:J5" si="2">E3-E4</f>
         <v>10505</v>
       </c>
       <c r="F5" s="8">
-        <f>F3-F4</f>
+        <f t="shared" si="2"/>
         <v>5662</v>
       </c>
       <c r="G5" s="8">
-        <f>G3-G4</f>
+        <f t="shared" si="2"/>
         <v>9631</v>
       </c>
       <c r="H5" s="8">
-        <f>H3-H4</f>
+        <f t="shared" si="2"/>
         <v>10571</v>
       </c>
       <c r="I5" s="8">
-        <f>I3-I4</f>
+        <f t="shared" si="2"/>
         <v>10044</v>
       </c>
       <c r="J5" s="8">
-        <f>J3-J4</f>
+        <f t="shared" si="2"/>
         <v>10675</v>
+      </c>
+      <c r="K5" s="8">
+        <f>K3*0.17</f>
+        <v>12239.864</v>
+      </c>
+      <c r="L5" s="8">
+        <f t="shared" ref="L5:U5" si="3">L3*0.17</f>
+        <v>12607.05992</v>
+      </c>
+      <c r="M5" s="8">
+        <f t="shared" si="3"/>
+        <v>12859.2011184</v>
+      </c>
+      <c r="N5" s="8">
+        <f t="shared" si="3"/>
+        <v>13116.385140768001</v>
+      </c>
+      <c r="O5" s="8">
+        <f t="shared" si="3"/>
+        <v>13378.71284358336</v>
+      </c>
+      <c r="P5" s="8">
+        <f t="shared" si="3"/>
+        <v>13646.287100455029</v>
+      </c>
+      <c r="Q5" s="8">
+        <f t="shared" si="3"/>
+        <v>13919.212842464129</v>
+      </c>
+      <c r="R5" s="8">
+        <f t="shared" si="3"/>
+        <v>14197.597099313412</v>
+      </c>
+      <c r="S5" s="8">
+        <f t="shared" si="3"/>
+        <v>14481.549041299682</v>
+      </c>
+      <c r="T5" s="8">
+        <f t="shared" si="3"/>
+        <v>14771.180022125674</v>
+      </c>
+      <c r="U5" s="8">
+        <f t="shared" si="3"/>
+        <v>15066.603622568187</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.3">
@@ -824,6 +1050,50 @@
       <c r="J6" s="6">
         <v>877</v>
       </c>
+      <c r="K6" s="6">
+        <f>K3*0.013</f>
+        <v>935.98959999999988</v>
+      </c>
+      <c r="L6" s="6">
+        <f t="shared" ref="L6:U6" si="4">L3*0.013</f>
+        <v>964.0692879999998</v>
+      </c>
+      <c r="M6" s="6">
+        <f t="shared" si="4"/>
+        <v>983.35067375999995</v>
+      </c>
+      <c r="N6" s="6">
+        <f t="shared" si="4"/>
+        <v>1003.0176872352</v>
+      </c>
+      <c r="O6" s="6">
+        <f t="shared" si="4"/>
+        <v>1023.0780409799039</v>
+      </c>
+      <c r="P6" s="6">
+        <f t="shared" si="4"/>
+        <v>1043.5396017995022</v>
+      </c>
+      <c r="Q6" s="6">
+        <f t="shared" si="4"/>
+        <v>1064.4103938354922</v>
+      </c>
+      <c r="R6" s="6">
+        <f t="shared" si="4"/>
+        <v>1085.6986017122019</v>
+      </c>
+      <c r="S6" s="6">
+        <f t="shared" si="4"/>
+        <v>1107.4125737464462</v>
+      </c>
+      <c r="T6" s="6">
+        <f t="shared" si="4"/>
+        <v>1129.5608252213751</v>
+      </c>
+      <c r="U6" s="6">
+        <f t="shared" si="4"/>
+        <v>1152.1520417258025</v>
+      </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -847,6 +1117,50 @@
       <c r="J7" s="6">
         <v>1744</v>
       </c>
+      <c r="K7" s="6">
+        <f>J7*1.04</f>
+        <v>1813.76</v>
+      </c>
+      <c r="L7" s="6">
+        <f>K7*1.03</f>
+        <v>1868.1728000000001</v>
+      </c>
+      <c r="M7" s="6">
+        <f>L7*1.02</f>
+        <v>1905.5362560000001</v>
+      </c>
+      <c r="N7" s="6">
+        <f t="shared" ref="N7:U7" si="5">M7*1.02</f>
+        <v>1943.6469811200002</v>
+      </c>
+      <c r="O7" s="6">
+        <f t="shared" si="5"/>
+        <v>1982.5199207424002</v>
+      </c>
+      <c r="P7" s="6">
+        <f t="shared" si="5"/>
+        <v>2022.1703191572483</v>
+      </c>
+      <c r="Q7" s="6">
+        <f t="shared" si="5"/>
+        <v>2062.6137255403933</v>
+      </c>
+      <c r="R7" s="6">
+        <f t="shared" si="5"/>
+        <v>2103.8660000512014</v>
+      </c>
+      <c r="S7" s="6">
+        <f t="shared" si="5"/>
+        <v>2145.9433200522253</v>
+      </c>
+      <c r="T7" s="6">
+        <f t="shared" si="5"/>
+        <v>2188.8621864532697</v>
+      </c>
+      <c r="U7" s="6">
+        <f t="shared" si="5"/>
+        <v>2232.6394301823352</v>
+      </c>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
@@ -870,34 +1184,122 @@
       <c r="J8" s="6">
         <v>3250</v>
       </c>
+      <c r="K8" s="6">
+        <f>J8*1.03</f>
+        <v>3347.5</v>
+      </c>
+      <c r="L8" s="6">
+        <f>K8*1.02</f>
+        <v>3414.4500000000003</v>
+      </c>
+      <c r="M8" s="6">
+        <f>L8*1.01</f>
+        <v>3448.5945000000002</v>
+      </c>
+      <c r="N8" s="6">
+        <f t="shared" ref="N8:U8" si="6">M8*1.01</f>
+        <v>3483.0804450000001</v>
+      </c>
+      <c r="O8" s="6">
+        <f t="shared" si="6"/>
+        <v>3517.91124945</v>
+      </c>
+      <c r="P8" s="6">
+        <f t="shared" si="6"/>
+        <v>3553.0903619444998</v>
+      </c>
+      <c r="Q8" s="6">
+        <f t="shared" si="6"/>
+        <v>3588.6212655639447</v>
+      </c>
+      <c r="R8" s="6">
+        <f t="shared" si="6"/>
+        <v>3624.5074782195843</v>
+      </c>
+      <c r="S8" s="6">
+        <f t="shared" si="6"/>
+        <v>3660.7525530017801</v>
+      </c>
+      <c r="T8" s="6">
+        <f t="shared" si="6"/>
+        <v>3697.3600785317981</v>
+      </c>
+      <c r="U8" s="6">
+        <f t="shared" si="6"/>
+        <v>3734.3336793171161</v>
+      </c>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="6">
-        <f>SUM(E6:E8)</f>
+        <f t="shared" ref="E9:K9" si="7">SUM(E6:E8)</f>
         <v>9483</v>
       </c>
       <c r="F9" s="6">
-        <f>SUM(F6:F8)</f>
+        <f t="shared" si="7"/>
         <v>4998</v>
       </c>
       <c r="G9" s="6">
-        <f>SUM(G6:G8)</f>
+        <f t="shared" si="7"/>
         <v>4798</v>
       </c>
       <c r="H9" s="6">
-        <f>SUM(H6:H8)</f>
+        <f t="shared" si="7"/>
         <v>5319</v>
       </c>
       <c r="I9" s="6">
-        <f>SUM(I6:I8)</f>
+        <f t="shared" si="7"/>
         <v>5778</v>
       </c>
       <c r="J9" s="6">
-        <f>SUM(J6:J8)</f>
+        <f t="shared" si="7"/>
         <v>5871</v>
+      </c>
+      <c r="K9" s="6">
+        <f t="shared" si="7"/>
+        <v>6097.2496000000001</v>
+      </c>
+      <c r="L9" s="6">
+        <f t="shared" ref="L9" si="8">SUM(L6:L8)</f>
+        <v>6246.6920879999998</v>
+      </c>
+      <c r="M9" s="6">
+        <f t="shared" ref="M9" si="9">SUM(M6:M8)</f>
+        <v>6337.4814297600005</v>
+      </c>
+      <c r="N9" s="6">
+        <f t="shared" ref="N9" si="10">SUM(N6:N8)</f>
+        <v>6429.7451133552004</v>
+      </c>
+      <c r="O9" s="6">
+        <f t="shared" ref="O9" si="11">SUM(O6:O8)</f>
+        <v>6523.5092111723043</v>
+      </c>
+      <c r="P9" s="6">
+        <f t="shared" ref="P9" si="12">SUM(P6:P8)</f>
+        <v>6618.8002829012503</v>
+      </c>
+      <c r="Q9" s="6">
+        <f t="shared" ref="Q9" si="13">SUM(Q6:Q8)</f>
+        <v>6715.6453849398304</v>
+      </c>
+      <c r="R9" s="6">
+        <f t="shared" ref="R9" si="14">SUM(R6:R8)</f>
+        <v>6814.0720799829878</v>
+      </c>
+      <c r="S9" s="6">
+        <f t="shared" ref="S9" si="15">SUM(S6:S8)</f>
+        <v>6914.1084468004519</v>
+      </c>
+      <c r="T9" s="6">
+        <f t="shared" ref="T9" si="16">SUM(T6:T8)</f>
+        <v>7015.7830902064434</v>
+      </c>
+      <c r="U9" s="6">
+        <f t="shared" ref="U9" si="17">SUM(U6:U8)</f>
+        <v>7119.1251512252538</v>
       </c>
     </row>
     <row r="10" spans="2:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -905,28 +1307,72 @@
         <v>26</v>
       </c>
       <c r="E10" s="8">
-        <f>E5-E9</f>
+        <f t="shared" ref="E10:K10" si="18">E5-E9</f>
         <v>1022</v>
       </c>
       <c r="F10" s="8">
-        <f>F5-F9</f>
+        <f t="shared" si="18"/>
         <v>664</v>
       </c>
       <c r="G10" s="8">
-        <f>G5-G9</f>
+        <f t="shared" si="18"/>
         <v>4833</v>
       </c>
       <c r="H10" s="8">
-        <f>H5-H9</f>
+        <f t="shared" si="18"/>
         <v>5252</v>
       </c>
       <c r="I10" s="8">
-        <f>I5-I9</f>
+        <f t="shared" si="18"/>
         <v>4266</v>
       </c>
       <c r="J10" s="8">
-        <f>J5-J9</f>
+        <f t="shared" si="18"/>
         <v>4804</v>
+      </c>
+      <c r="K10" s="8">
+        <f t="shared" si="18"/>
+        <v>6142.6143999999995</v>
+      </c>
+      <c r="L10" s="8">
+        <f t="shared" ref="L10" si="19">L5-L9</f>
+        <v>6360.3678319999999</v>
+      </c>
+      <c r="M10" s="8">
+        <f t="shared" ref="M10" si="20">M5-M9</f>
+        <v>6521.7196886399997</v>
+      </c>
+      <c r="N10" s="8">
+        <f t="shared" ref="N10" si="21">N5-N9</f>
+        <v>6686.6400274128009</v>
+      </c>
+      <c r="O10" s="8">
+        <f t="shared" ref="O10" si="22">O5-O9</f>
+        <v>6855.2036324110559</v>
+      </c>
+      <c r="P10" s="8">
+        <f t="shared" ref="P10" si="23">P5-P9</f>
+        <v>7027.4868175537786</v>
+      </c>
+      <c r="Q10" s="8">
+        <f t="shared" ref="Q10" si="24">Q5-Q9</f>
+        <v>7203.5674575242983</v>
+      </c>
+      <c r="R10" s="8">
+        <f t="shared" ref="R10" si="25">R5-R9</f>
+        <v>7383.5250193304246</v>
+      </c>
+      <c r="S10" s="8">
+        <f t="shared" ref="S10" si="26">S5-S9</f>
+        <v>7567.4405944992304</v>
+      </c>
+      <c r="T10" s="8">
+        <f t="shared" ref="T10" si="27">T5-T9</f>
+        <v>7755.3969319192311</v>
+      </c>
+      <c r="U10" s="8">
+        <f t="shared" ref="U10" si="28">U5-U9</f>
+        <v>7947.4784713429335</v>
       </c>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.3">
@@ -951,6 +1397,50 @@
       <c r="J11" s="6">
         <v>-303</v>
       </c>
+      <c r="K11" s="6">
+        <f>J11*1.01</f>
+        <v>-306.03000000000003</v>
+      </c>
+      <c r="L11" s="6">
+        <f t="shared" ref="L11:U11" si="29">K11*1.01</f>
+        <v>-309.09030000000001</v>
+      </c>
+      <c r="M11" s="6">
+        <f t="shared" si="29"/>
+        <v>-312.18120300000004</v>
+      </c>
+      <c r="N11" s="6">
+        <f t="shared" si="29"/>
+        <v>-315.30301503000004</v>
+      </c>
+      <c r="O11" s="6">
+        <f t="shared" si="29"/>
+        <v>-318.45604518030007</v>
+      </c>
+      <c r="P11" s="6">
+        <f t="shared" si="29"/>
+        <v>-321.64060563210307</v>
+      </c>
+      <c r="Q11" s="6">
+        <f t="shared" si="29"/>
+        <v>-324.85701168842411</v>
+      </c>
+      <c r="R11" s="6">
+        <f t="shared" si="29"/>
+        <v>-328.10558180530836</v>
+      </c>
+      <c r="S11" s="6">
+        <f t="shared" si="29"/>
+        <v>-331.38663762336142</v>
+      </c>
+      <c r="T11" s="6">
+        <f t="shared" si="29"/>
+        <v>-334.70050399959501</v>
+      </c>
+      <c r="U11" s="6">
+        <f t="shared" si="29"/>
+        <v>-338.04750903959098</v>
+      </c>
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
@@ -974,6 +1464,50 @@
       <c r="J12" s="6">
         <v>197</v>
       </c>
+      <c r="K12" s="6">
+        <f>J12*1.01</f>
+        <v>198.97</v>
+      </c>
+      <c r="L12" s="6">
+        <f t="shared" ref="L12:U12" si="30">K12*1.01</f>
+        <v>200.9597</v>
+      </c>
+      <c r="M12" s="6">
+        <f t="shared" si="30"/>
+        <v>202.96929700000001</v>
+      </c>
+      <c r="N12" s="6">
+        <f t="shared" si="30"/>
+        <v>204.99898997000003</v>
+      </c>
+      <c r="O12" s="6">
+        <f t="shared" si="30"/>
+        <v>207.04897986970002</v>
+      </c>
+      <c r="P12" s="6">
+        <f t="shared" si="30"/>
+        <v>209.11946966839702</v>
+      </c>
+      <c r="Q12" s="6">
+        <f t="shared" si="30"/>
+        <v>211.21066436508099</v>
+      </c>
+      <c r="R12" s="6">
+        <f t="shared" si="30"/>
+        <v>213.32277100873179</v>
+      </c>
+      <c r="S12" s="6">
+        <f t="shared" si="30"/>
+        <v>215.4559987188191</v>
+      </c>
+      <c r="T12" s="6">
+        <f t="shared" si="30"/>
+        <v>217.61055870600728</v>
+      </c>
+      <c r="U12" s="6">
+        <f t="shared" si="30"/>
+        <v>219.78666429306736</v>
+      </c>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
@@ -997,6 +1531,50 @@
       <c r="J13" s="6">
         <v>-350</v>
       </c>
+      <c r="K13" s="6">
+        <f>J13*1.01</f>
+        <v>-353.5</v>
+      </c>
+      <c r="L13" s="6">
+        <f t="shared" ref="L13:U13" si="31">K13*1.01</f>
+        <v>-357.03500000000003</v>
+      </c>
+      <c r="M13" s="6">
+        <f t="shared" si="31"/>
+        <v>-360.60535000000004</v>
+      </c>
+      <c r="N13" s="6">
+        <f t="shared" si="31"/>
+        <v>-364.21140350000007</v>
+      </c>
+      <c r="O13" s="6">
+        <f t="shared" si="31"/>
+        <v>-367.85351753500009</v>
+      </c>
+      <c r="P13" s="6">
+        <f t="shared" si="31"/>
+        <v>-371.53205271035011</v>
+      </c>
+      <c r="Q13" s="6">
+        <f t="shared" si="31"/>
+        <v>-375.24737323745364</v>
+      </c>
+      <c r="R13" s="6">
+        <f t="shared" si="31"/>
+        <v>-378.99984696982818</v>
+      </c>
+      <c r="S13" s="6">
+        <f t="shared" si="31"/>
+        <v>-382.78984543952646</v>
+      </c>
+      <c r="T13" s="6">
+        <f t="shared" si="31"/>
+        <v>-386.61774389392173</v>
+      </c>
+      <c r="U13" s="6">
+        <f t="shared" si="31"/>
+        <v>-390.48392133286097</v>
+      </c>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
@@ -1020,6 +1598,50 @@
       <c r="J14" s="6">
         <v>-44</v>
       </c>
+      <c r="K14" s="6">
+        <f>J14*1.01</f>
+        <v>-44.44</v>
+      </c>
+      <c r="L14" s="6">
+        <f t="shared" ref="L14:U14" si="32">K14*1.01</f>
+        <v>-44.884399999999999</v>
+      </c>
+      <c r="M14" s="6">
+        <f t="shared" si="32"/>
+        <v>-45.333244000000001</v>
+      </c>
+      <c r="N14" s="6">
+        <f t="shared" si="32"/>
+        <v>-45.786576439999997</v>
+      </c>
+      <c r="O14" s="6">
+        <f t="shared" si="32"/>
+        <v>-46.244442204399995</v>
+      </c>
+      <c r="P14" s="6">
+        <f t="shared" si="32"/>
+        <v>-46.706886626443996</v>
+      </c>
+      <c r="Q14" s="6">
+        <f t="shared" si="32"/>
+        <v>-47.173955492708437</v>
+      </c>
+      <c r="R14" s="6">
+        <f t="shared" si="32"/>
+        <v>-47.64569504763552</v>
+      </c>
+      <c r="S14" s="6">
+        <f t="shared" si="32"/>
+        <v>-48.122151998111875</v>
+      </c>
+      <c r="T14" s="6">
+        <f t="shared" si="32"/>
+        <v>-48.603373518092994</v>
+      </c>
+      <c r="U14" s="6">
+        <f t="shared" si="32"/>
+        <v>-49.089407253273926</v>
+      </c>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
@@ -1043,6 +1665,50 @@
       <c r="J15" s="6">
         <v>-802</v>
       </c>
+      <c r="K15" s="6">
+        <f>J15*1.01</f>
+        <v>-810.02</v>
+      </c>
+      <c r="L15" s="6">
+        <f t="shared" ref="L15:U15" si="33">K15*1.01</f>
+        <v>-818.12019999999995</v>
+      </c>
+      <c r="M15" s="6">
+        <f t="shared" si="33"/>
+        <v>-826.30140199999994</v>
+      </c>
+      <c r="N15" s="6">
+        <f t="shared" si="33"/>
+        <v>-834.56441601999995</v>
+      </c>
+      <c r="O15" s="6">
+        <f t="shared" si="33"/>
+        <v>-842.91006018019993</v>
+      </c>
+      <c r="P15" s="6">
+        <f t="shared" si="33"/>
+        <v>-851.33916078200195</v>
+      </c>
+      <c r="Q15" s="6">
+        <f t="shared" si="33"/>
+        <v>-859.85255238982199</v>
+      </c>
+      <c r="R15" s="6">
+        <f t="shared" si="33"/>
+        <v>-868.45107791372027</v>
+      </c>
+      <c r="S15" s="6">
+        <f t="shared" si="33"/>
+        <v>-877.13558869285748</v>
+      </c>
+      <c r="T15" s="6">
+        <f t="shared" si="33"/>
+        <v>-885.90694457978611</v>
+      </c>
+      <c r="U15" s="6">
+        <f t="shared" si="33"/>
+        <v>-894.76601402558401</v>
+      </c>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
@@ -1066,8 +1732,52 @@
       <c r="J16" s="6">
         <v>900</v>
       </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K16" s="6">
+        <f>J16*1.01</f>
+        <v>909</v>
+      </c>
+      <c r="L16" s="6">
+        <f t="shared" ref="L16:U16" si="34">K16*1.01</f>
+        <v>918.09</v>
+      </c>
+      <c r="M16" s="6">
+        <f t="shared" si="34"/>
+        <v>927.2709000000001</v>
+      </c>
+      <c r="N16" s="6">
+        <f t="shared" si="34"/>
+        <v>936.54360900000006</v>
+      </c>
+      <c r="O16" s="6">
+        <f t="shared" si="34"/>
+        <v>945.90904509000006</v>
+      </c>
+      <c r="P16" s="6">
+        <f t="shared" si="34"/>
+        <v>955.36813554090008</v>
+      </c>
+      <c r="Q16" s="6">
+        <f t="shared" si="34"/>
+        <v>964.92181689630911</v>
+      </c>
+      <c r="R16" s="6">
+        <f t="shared" si="34"/>
+        <v>974.57103506527221</v>
+      </c>
+      <c r="S16" s="6">
+        <f t="shared" si="34"/>
+        <v>984.31674541592497</v>
+      </c>
+      <c r="T16" s="6">
+        <f t="shared" si="34"/>
+        <v>994.15991287008421</v>
+      </c>
+      <c r="U16" s="6">
+        <f t="shared" si="34"/>
+        <v>1004.1015119987851</v>
+      </c>
+    </row>
+    <row r="17" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>32</v>
       </c>
@@ -1089,66 +1799,187 @@
       <c r="J17" s="6">
         <v>-219</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="6">
+        <v>0</v>
+      </c>
+      <c r="L17" s="6">
+        <v>0</v>
+      </c>
+      <c r="M17" s="6">
+        <v>0</v>
+      </c>
+      <c r="N17" s="6">
+        <v>0</v>
+      </c>
+      <c r="O17" s="6">
+        <v>0</v>
+      </c>
+      <c r="P17" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>0</v>
+      </c>
+      <c r="R17" s="6">
+        <v>0</v>
+      </c>
+      <c r="S17" s="6">
+        <v>0</v>
+      </c>
+      <c r="T17" s="6">
+        <v>0</v>
+      </c>
+      <c r="U17" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="6">
-        <f>SUM(E11:E17)</f>
+        <f t="shared" ref="E18:K18" si="35">SUM(E11:E17)</f>
         <v>-42</v>
       </c>
       <c r="F18" s="6">
-        <f>SUM(F11:F17)</f>
+        <f t="shared" si="35"/>
         <v>1794</v>
       </c>
       <c r="G18" s="6">
-        <f>SUM(G11:G17)</f>
+        <f t="shared" si="35"/>
         <v>-194</v>
       </c>
       <c r="H18" s="6">
-        <f>SUM(H11:H17)</f>
+        <f t="shared" si="35"/>
         <v>177</v>
       </c>
       <c r="I18" s="6">
-        <f>SUM(I11:I17)</f>
+        <f t="shared" si="35"/>
         <v>-503</v>
       </c>
       <c r="J18" s="6">
-        <f>SUM(J11:J17)</f>
+        <f t="shared" si="35"/>
         <v>-621</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K18" s="6">
+        <f t="shared" si="35"/>
+        <v>-406.02</v>
+      </c>
+      <c r="L18" s="6">
+        <f t="shared" ref="L18" si="36">SUM(L11:L17)</f>
+        <v>-410.08019999999999</v>
+      </c>
+      <c r="M18" s="6">
+        <f t="shared" ref="M18" si="37">SUM(M11:M17)</f>
+        <v>-414.18100199999992</v>
+      </c>
+      <c r="N18" s="6">
+        <f t="shared" ref="N18" si="38">SUM(N11:N17)</f>
+        <v>-418.3228120199999</v>
+      </c>
+      <c r="O18" s="6">
+        <f t="shared" ref="O18" si="39">SUM(O11:O17)</f>
+        <v>-422.50604014019996</v>
+      </c>
+      <c r="P18" s="6">
+        <f t="shared" ref="P18" si="40">SUM(P11:P17)</f>
+        <v>-426.73110054160202</v>
+      </c>
+      <c r="Q18" s="6">
+        <f t="shared" ref="Q18" si="41">SUM(Q11:Q17)</f>
+        <v>-430.99841154701812</v>
+      </c>
+      <c r="R18" s="6">
+        <f t="shared" ref="R18" si="42">SUM(R11:R17)</f>
+        <v>-435.30839566248835</v>
+      </c>
+      <c r="S18" s="6">
+        <f t="shared" ref="S18" si="43">SUM(S11:S17)</f>
+        <v>-439.66147961911315</v>
+      </c>
+      <c r="T18" s="6">
+        <f t="shared" ref="T18" si="44">SUM(T11:T17)</f>
+        <v>-444.05809441530425</v>
+      </c>
+      <c r="U18" s="6">
+        <f t="shared" ref="U18" si="45">SUM(U11:U17)</f>
+        <v>-448.49867535945759</v>
+      </c>
+    </row>
+    <row r="19" spans="2:135" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E19" s="8">
-        <f>E10-E18</f>
+        <f t="shared" ref="E19:K19" si="46">E10-E18</f>
         <v>1064</v>
       </c>
       <c r="F19" s="8">
-        <f>F10-F18</f>
+        <f t="shared" si="46"/>
         <v>-1130</v>
       </c>
       <c r="G19" s="8">
-        <f>G10-G18</f>
+        <f t="shared" si="46"/>
         <v>5027</v>
       </c>
       <c r="H19" s="8">
-        <f>H10-H18</f>
+        <f t="shared" si="46"/>
         <v>5075</v>
       </c>
       <c r="I19" s="8">
-        <f>I10-I18</f>
+        <f t="shared" si="46"/>
         <v>4769</v>
       </c>
       <c r="J19" s="8">
-        <f>J10-J18</f>
+        <f t="shared" si="46"/>
         <v>5425</v>
       </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K19" s="8">
+        <f t="shared" si="46"/>
+        <v>6548.634399999999</v>
+      </c>
+      <c r="L19" s="8">
+        <f t="shared" ref="L19" si="47">L10-L18</f>
+        <v>6770.4480320000002</v>
+      </c>
+      <c r="M19" s="8">
+        <f t="shared" ref="M19" si="48">M10-M18</f>
+        <v>6935.90069064</v>
+      </c>
+      <c r="N19" s="8">
+        <f t="shared" ref="N19" si="49">N10-N18</f>
+        <v>7104.962839432801</v>
+      </c>
+      <c r="O19" s="8">
+        <f t="shared" ref="O19" si="50">O10-O18</f>
+        <v>7277.7096725512556</v>
+      </c>
+      <c r="P19" s="8">
+        <f t="shared" ref="P19" si="51">P10-P18</f>
+        <v>7454.2179180953808</v>
+      </c>
+      <c r="Q19" s="8">
+        <f t="shared" ref="Q19" si="52">Q10-Q18</f>
+        <v>7634.5658690713162</v>
+      </c>
+      <c r="R19" s="8">
+        <f t="shared" ref="R19" si="53">R10-R18</f>
+        <v>7818.8334149929133</v>
+      </c>
+      <c r="S19" s="8">
+        <f t="shared" ref="S19" si="54">S10-S18</f>
+        <v>8007.1020741183438</v>
+      </c>
+      <c r="T19" s="8">
+        <f t="shared" ref="T19" si="55">T10-T18</f>
+        <v>8199.4550263345354</v>
+      </c>
+      <c r="U19" s="8">
+        <f t="shared" ref="U19" si="56">U10-U18</f>
+        <v>8395.9771467023911</v>
+      </c>
+    </row>
+    <row r="20" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>28</v>
       </c>
@@ -1170,8 +2001,52 @@
       <c r="J20" s="6">
         <v>1347</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K20" s="6">
+        <f>K19*0.23</f>
+        <v>1506.1859119999999</v>
+      </c>
+      <c r="L20" s="6">
+        <f t="shared" ref="L20:U20" si="57">L19*0.23</f>
+        <v>1557.20304736</v>
+      </c>
+      <c r="M20" s="6">
+        <f t="shared" si="57"/>
+        <v>1595.2571588472001</v>
+      </c>
+      <c r="N20" s="6">
+        <f t="shared" si="57"/>
+        <v>1634.1414530695442</v>
+      </c>
+      <c r="O20" s="6">
+        <f t="shared" si="57"/>
+        <v>1673.8732246867889</v>
+      </c>
+      <c r="P20" s="6">
+        <f t="shared" si="57"/>
+        <v>1714.4701211619376</v>
+      </c>
+      <c r="Q20" s="6">
+        <f t="shared" si="57"/>
+        <v>1755.9501498864029</v>
+      </c>
+      <c r="R20" s="6">
+        <f t="shared" si="57"/>
+        <v>1798.3316854483701</v>
+      </c>
+      <c r="S20" s="6">
+        <f t="shared" si="57"/>
+        <v>1841.6334770472192</v>
+      </c>
+      <c r="T20" s="6">
+        <f t="shared" si="57"/>
+        <v>1885.8746560569432</v>
+      </c>
+      <c r="U20" s="6">
+        <f t="shared" si="57"/>
+        <v>1931.07474374155</v>
+      </c>
+    </row>
+    <row r="21" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>29</v>
       </c>
@@ -1193,37 +2068,581 @@
       <c r="J21" s="6">
         <v>-154</v>
       </c>
-    </row>
-    <row r="22" spans="2:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K21" s="6">
+        <f>-K19*0.03</f>
+        <v>-196.45903199999995</v>
+      </c>
+      <c r="L21" s="6">
+        <f t="shared" ref="L21:U21" si="58">-L19*0.03</f>
+        <v>-203.11344095999999</v>
+      </c>
+      <c r="M21" s="6">
+        <f t="shared" si="58"/>
+        <v>-208.07702071919999</v>
+      </c>
+      <c r="N21" s="6">
+        <f t="shared" si="58"/>
+        <v>-213.14888518298403</v>
+      </c>
+      <c r="O21" s="6">
+        <f t="shared" si="58"/>
+        <v>-218.33129017653766</v>
+      </c>
+      <c r="P21" s="6">
+        <f t="shared" si="58"/>
+        <v>-223.62653754286143</v>
+      </c>
+      <c r="Q21" s="6">
+        <f t="shared" si="58"/>
+        <v>-229.03697607213948</v>
+      </c>
+      <c r="R21" s="6">
+        <f t="shared" si="58"/>
+        <v>-234.56500244978739</v>
+      </c>
+      <c r="S21" s="6">
+        <f t="shared" si="58"/>
+        <v>-240.21306222355031</v>
+      </c>
+      <c r="T21" s="6">
+        <f t="shared" si="58"/>
+        <v>-245.98365079003605</v>
+      </c>
+      <c r="U21" s="6">
+        <f t="shared" si="58"/>
+        <v>-251.87931440107172</v>
+      </c>
+    </row>
+    <row r="22" spans="2:135" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E22" s="8">
-        <f>E19-E20-E21</f>
+        <f t="shared" ref="E22:K22" si="59">E19-E20-E21</f>
         <v>-1362</v>
       </c>
       <c r="F22" s="8">
-        <f>F19-F20-F21</f>
+        <f t="shared" si="59"/>
         <v>-1133</v>
       </c>
       <c r="G22" s="8">
-        <f>G19-G20-G21</f>
+        <f t="shared" si="59"/>
         <v>4213</v>
       </c>
       <c r="H22" s="8">
-        <f>H19-H20-H21</f>
+        <f t="shared" si="59"/>
         <v>4247</v>
       </c>
       <c r="I22" s="8">
-        <f>I19-I20-I21</f>
+        <f t="shared" si="59"/>
         <v>3789</v>
       </c>
       <c r="J22" s="8">
-        <f>J19-J20-J21</f>
+        <f t="shared" si="59"/>
         <v>4232</v>
       </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K22" s="8">
+        <f t="shared" si="59"/>
+        <v>5238.9075199999988</v>
+      </c>
+      <c r="L22" s="8">
+        <f t="shared" ref="L22" si="60">L19-L20-L21</f>
+        <v>5416.3584256000004</v>
+      </c>
+      <c r="M22" s="8">
+        <f t="shared" ref="M22" si="61">M19-M20-M21</f>
+        <v>5548.7205525119998</v>
+      </c>
+      <c r="N22" s="8">
+        <f t="shared" ref="N22" si="62">N19-N20-N21</f>
+        <v>5683.9702715462408</v>
+      </c>
+      <c r="O22" s="8">
+        <f t="shared" ref="O22" si="63">O19-O20-O21</f>
+        <v>5822.1677380410047</v>
+      </c>
+      <c r="P22" s="8">
+        <f t="shared" ref="P22" si="64">P19-P20-P21</f>
+        <v>5963.3743344763043</v>
+      </c>
+      <c r="Q22" s="8">
+        <f t="shared" ref="Q22" si="65">Q19-Q20-Q21</f>
+        <v>6107.652695257053</v>
+      </c>
+      <c r="R22" s="8">
+        <f t="shared" ref="R22" si="66">R19-R20-R21</f>
+        <v>6255.0667319943304</v>
+      </c>
+      <c r="S22" s="8">
+        <f t="shared" ref="S22" si="67">S19-S20-S21</f>
+        <v>6405.6816592946743</v>
+      </c>
+      <c r="T22" s="8">
+        <f t="shared" ref="T22" si="68">T19-T20-T21</f>
+        <v>6559.5640210676283</v>
+      </c>
+      <c r="U22" s="8">
+        <f t="shared" ref="U22" si="69">U19-U20-U21</f>
+        <v>6716.7817173619123</v>
+      </c>
+      <c r="V22" s="2">
+        <f>U22*(1+$Y$27)</f>
+        <v>6649.613900188293</v>
+      </c>
+      <c r="W22" s="2">
+        <f t="shared" ref="W22:CH22" si="70">V22*(1+$Y$27)</f>
+        <v>6583.1177611864096</v>
+      </c>
+      <c r="X22" s="2">
+        <f t="shared" si="70"/>
+        <v>6517.2865835745451</v>
+      </c>
+      <c r="Y22" s="2">
+        <f t="shared" si="70"/>
+        <v>6452.1137177388</v>
+      </c>
+      <c r="Z22" s="2">
+        <f t="shared" si="70"/>
+        <v>6387.5925805614115</v>
+      </c>
+      <c r="AA22" s="2">
+        <f t="shared" si="70"/>
+        <v>6323.7166547557972</v>
+      </c>
+      <c r="AB22" s="2">
+        <f t="shared" si="70"/>
+        <v>6260.4794882082388</v>
+      </c>
+      <c r="AC22" s="2">
+        <f t="shared" si="70"/>
+        <v>6197.8746933261564</v>
+      </c>
+      <c r="AD22" s="2">
+        <f t="shared" si="70"/>
+        <v>6135.895946392895</v>
+      </c>
+      <c r="AE22" s="2">
+        <f t="shared" si="70"/>
+        <v>6074.5369869289661</v>
+      </c>
+      <c r="AF22" s="2">
+        <f t="shared" si="70"/>
+        <v>6013.7916170596764</v>
+      </c>
+      <c r="AG22" s="2">
+        <f t="shared" si="70"/>
+        <v>5953.6537008890791</v>
+      </c>
+      <c r="AH22" s="2">
+        <f t="shared" si="70"/>
+        <v>5894.1171638801879</v>
+      </c>
+      <c r="AI22" s="2">
+        <f t="shared" si="70"/>
+        <v>5835.1759922413858</v>
+      </c>
+      <c r="AJ22" s="2">
+        <f t="shared" si="70"/>
+        <v>5776.8242323189716</v>
+      </c>
+      <c r="AK22" s="2">
+        <f t="shared" si="70"/>
+        <v>5719.0559899957816</v>
+      </c>
+      <c r="AL22" s="2">
+        <f t="shared" si="70"/>
+        <v>5661.8654300958233</v>
+      </c>
+      <c r="AM22" s="2">
+        <f t="shared" si="70"/>
+        <v>5605.2467757948652</v>
+      </c>
+      <c r="AN22" s="2">
+        <f t="shared" si="70"/>
+        <v>5549.1943080369165</v>
+      </c>
+      <c r="AO22" s="2">
+        <f t="shared" si="70"/>
+        <v>5493.7023649565472</v>
+      </c>
+      <c r="AP22" s="2">
+        <f t="shared" si="70"/>
+        <v>5438.765341306982</v>
+      </c>
+      <c r="AQ22" s="2">
+        <f t="shared" si="70"/>
+        <v>5384.3776878939125</v>
+      </c>
+      <c r="AR22" s="2">
+        <f t="shared" si="70"/>
+        <v>5330.5339110149735</v>
+      </c>
+      <c r="AS22" s="2">
+        <f t="shared" si="70"/>
+        <v>5277.2285719048241</v>
+      </c>
+      <c r="AT22" s="2">
+        <f t="shared" si="70"/>
+        <v>5224.4562861857758</v>
+      </c>
+      <c r="AU22" s="2">
+        <f t="shared" si="70"/>
+        <v>5172.2117233239178</v>
+      </c>
+      <c r="AV22" s="2">
+        <f t="shared" si="70"/>
+        <v>5120.4896060906785</v>
+      </c>
+      <c r="AW22" s="2">
+        <f t="shared" si="70"/>
+        <v>5069.2847100297713</v>
+      </c>
+      <c r="AX22" s="2">
+        <f t="shared" si="70"/>
+        <v>5018.5918629294738</v>
+      </c>
+      <c r="AY22" s="2">
+        <f t="shared" si="70"/>
+        <v>4968.4059443001788</v>
+      </c>
+      <c r="AZ22" s="2">
+        <f t="shared" si="70"/>
+        <v>4918.7218848571774</v>
+      </c>
+      <c r="BA22" s="2">
+        <f t="shared" si="70"/>
+        <v>4869.5346660086052</v>
+      </c>
+      <c r="BB22" s="2">
+        <f t="shared" si="70"/>
+        <v>4820.839319348519</v>
+      </c>
+      <c r="BC22" s="2">
+        <f t="shared" si="70"/>
+        <v>4772.6309261550341</v>
+      </c>
+      <c r="BD22" s="2">
+        <f t="shared" si="70"/>
+        <v>4724.9046168934838</v>
+      </c>
+      <c r="BE22" s="2">
+        <f t="shared" si="70"/>
+        <v>4677.6555707245489</v>
+      </c>
+      <c r="BF22" s="2">
+        <f t="shared" si="70"/>
+        <v>4630.8790150173036</v>
+      </c>
+      <c r="BG22" s="2">
+        <f t="shared" si="70"/>
+        <v>4584.5702248671305</v>
+      </c>
+      <c r="BH22" s="2">
+        <f t="shared" si="70"/>
+        <v>4538.7245226184596</v>
+      </c>
+      <c r="BI22" s="2">
+        <f t="shared" si="70"/>
+        <v>4493.3372773922747</v>
+      </c>
+      <c r="BJ22" s="2">
+        <f t="shared" si="70"/>
+        <v>4448.4039046183516</v>
+      </c>
+      <c r="BK22" s="2">
+        <f t="shared" si="70"/>
+        <v>4403.9198655721684</v>
+      </c>
+      <c r="BL22" s="2">
+        <f t="shared" si="70"/>
+        <v>4359.8806669164469</v>
+      </c>
+      <c r="BM22" s="2">
+        <f t="shared" si="70"/>
+        <v>4316.2818602472826</v>
+      </c>
+      <c r="BN22" s="2">
+        <f t="shared" si="70"/>
+        <v>4273.1190416448098</v>
+      </c>
+      <c r="BO22" s="2">
+        <f t="shared" si="70"/>
+        <v>4230.3878512283618</v>
+      </c>
+      <c r="BP22" s="2">
+        <f t="shared" si="70"/>
+        <v>4188.0839727160783</v>
+      </c>
+      <c r="BQ22" s="2">
+        <f t="shared" si="70"/>
+        <v>4146.2031329889178</v>
+      </c>
+      <c r="BR22" s="2">
+        <f t="shared" si="70"/>
+        <v>4104.7411016590286</v>
+      </c>
+      <c r="BS22" s="2">
+        <f t="shared" si="70"/>
+        <v>4063.6936906424385</v>
+      </c>
+      <c r="BT22" s="2">
+        <f t="shared" si="70"/>
+        <v>4023.0567537360139</v>
+      </c>
+      <c r="BU22" s="2">
+        <f t="shared" si="70"/>
+        <v>3982.8261861986539</v>
+      </c>
+      <c r="BV22" s="2">
+        <f t="shared" si="70"/>
+        <v>3942.9979243366674</v>
+      </c>
+      <c r="BW22" s="2">
+        <f t="shared" si="70"/>
+        <v>3903.5679450933008</v>
+      </c>
+      <c r="BX22" s="2">
+        <f t="shared" si="70"/>
+        <v>3864.5322656423677</v>
+      </c>
+      <c r="BY22" s="2">
+        <f t="shared" si="70"/>
+        <v>3825.8869429859442</v>
+      </c>
+      <c r="BZ22" s="2">
+        <f t="shared" si="70"/>
+        <v>3787.6280735560849</v>
+      </c>
+      <c r="CA22" s="2">
+        <f t="shared" si="70"/>
+        <v>3749.7517928205239</v>
+      </c>
+      <c r="CB22" s="2">
+        <f t="shared" si="70"/>
+        <v>3712.2542748923188</v>
+      </c>
+      <c r="CC22" s="2">
+        <f t="shared" si="70"/>
+        <v>3675.1317321433958</v>
+      </c>
+      <c r="CD22" s="2">
+        <f t="shared" si="70"/>
+        <v>3638.3804148219619</v>
+      </c>
+      <c r="CE22" s="2">
+        <f t="shared" si="70"/>
+        <v>3601.9966106737425</v>
+      </c>
+      <c r="CF22" s="2">
+        <f t="shared" si="70"/>
+        <v>3565.9766445670048</v>
+      </c>
+      <c r="CG22" s="2">
+        <f t="shared" si="70"/>
+        <v>3530.3168781213349</v>
+      </c>
+      <c r="CH22" s="2">
+        <f t="shared" si="70"/>
+        <v>3495.0137093401213</v>
+      </c>
+      <c r="CI22" s="2">
+        <f t="shared" ref="CI22:EE22" si="71">CH22*(1+$Y$27)</f>
+        <v>3460.06357224672</v>
+      </c>
+      <c r="CJ22" s="2">
+        <f t="shared" si="71"/>
+        <v>3425.4629365242527</v>
+      </c>
+      <c r="CK22" s="2">
+        <f t="shared" si="71"/>
+        <v>3391.20830715901</v>
+      </c>
+      <c r="CL22" s="2">
+        <f t="shared" si="71"/>
+        <v>3357.2962240874199</v>
+      </c>
+      <c r="CM22" s="2">
+        <f t="shared" si="71"/>
+        <v>3323.7232618465455</v>
+      </c>
+      <c r="CN22" s="2">
+        <f t="shared" si="71"/>
+        <v>3290.48602922808</v>
+      </c>
+      <c r="CO22" s="2">
+        <f t="shared" si="71"/>
+        <v>3257.5811689357993</v>
+      </c>
+      <c r="CP22" s="2">
+        <f t="shared" si="71"/>
+        <v>3225.0053572464412</v>
+      </c>
+      <c r="CQ22" s="2">
+        <f t="shared" si="71"/>
+        <v>3192.7553036739769</v>
+      </c>
+      <c r="CR22" s="2">
+        <f t="shared" si="71"/>
+        <v>3160.8277506372369</v>
+      </c>
+      <c r="CS22" s="2">
+        <f t="shared" si="71"/>
+        <v>3129.2194731308646</v>
+      </c>
+      <c r="CT22" s="2">
+        <f t="shared" si="71"/>
+        <v>3097.9272783995557</v>
+      </c>
+      <c r="CU22" s="2">
+        <f t="shared" si="71"/>
+        <v>3066.9480056155603</v>
+      </c>
+      <c r="CV22" s="2">
+        <f t="shared" si="71"/>
+        <v>3036.2785255594049</v>
+      </c>
+      <c r="CW22" s="2">
+        <f t="shared" si="71"/>
+        <v>3005.9157403038107</v>
+      </c>
+      <c r="CX22" s="2">
+        <f t="shared" si="71"/>
+        <v>2975.8565829007725</v>
+      </c>
+      <c r="CY22" s="2">
+        <f t="shared" si="71"/>
+        <v>2946.0980170717648</v>
+      </c>
+      <c r="CZ22" s="2">
+        <f t="shared" si="71"/>
+        <v>2916.6370369010474</v>
+      </c>
+      <c r="DA22" s="2">
+        <f t="shared" si="71"/>
+        <v>2887.4706665320368</v>
+      </c>
+      <c r="DB22" s="2">
+        <f t="shared" si="71"/>
+        <v>2858.5959598667164</v>
+      </c>
+      <c r="DC22" s="2">
+        <f t="shared" si="71"/>
+        <v>2830.0100002680492</v>
+      </c>
+      <c r="DD22" s="2">
+        <f t="shared" si="71"/>
+        <v>2801.7099002653686</v>
+      </c>
+      <c r="DE22" s="2">
+        <f t="shared" si="71"/>
+        <v>2773.692801262715</v>
+      </c>
+      <c r="DF22" s="2">
+        <f t="shared" si="71"/>
+        <v>2745.9558732500877</v>
+      </c>
+      <c r="DG22" s="2">
+        <f t="shared" si="71"/>
+        <v>2718.4963145175871</v>
+      </c>
+      <c r="DH22" s="2">
+        <f t="shared" si="71"/>
+        <v>2691.3113513724111</v>
+      </c>
+      <c r="DI22" s="2">
+        <f t="shared" si="71"/>
+        <v>2664.398237858687</v>
+      </c>
+      <c r="DJ22" s="2">
+        <f t="shared" si="71"/>
+        <v>2637.7542554801003</v>
+      </c>
+      <c r="DK22" s="2">
+        <f t="shared" si="71"/>
+        <v>2611.3767129252992</v>
+      </c>
+      <c r="DL22" s="2">
+        <f t="shared" si="71"/>
+        <v>2585.2629457960461</v>
+      </c>
+      <c r="DM22" s="2">
+        <f t="shared" si="71"/>
+        <v>2559.4103163380855</v>
+      </c>
+      <c r="DN22" s="2">
+        <f t="shared" si="71"/>
+        <v>2533.8162131747044</v>
+      </c>
+      <c r="DO22" s="2">
+        <f t="shared" si="71"/>
+        <v>2508.4780510429573</v>
+      </c>
+      <c r="DP22" s="2">
+        <f t="shared" si="71"/>
+        <v>2483.3932705325278</v>
+      </c>
+      <c r="DQ22" s="2">
+        <f t="shared" si="71"/>
+        <v>2458.5593378272024</v>
+      </c>
+      <c r="DR22" s="2">
+        <f t="shared" si="71"/>
+        <v>2433.9737444489306</v>
+      </c>
+      <c r="DS22" s="2">
+        <f t="shared" si="71"/>
+        <v>2409.6340070044412</v>
+      </c>
+      <c r="DT22" s="2">
+        <f t="shared" si="71"/>
+        <v>2385.5376669343968</v>
+      </c>
+      <c r="DU22" s="2">
+        <f t="shared" si="71"/>
+        <v>2361.6822902650529</v>
+      </c>
+      <c r="DV22" s="2">
+        <f t="shared" si="71"/>
+        <v>2338.0654673624022</v>
+      </c>
+      <c r="DW22" s="2">
+        <f t="shared" si="71"/>
+        <v>2314.684812688778</v>
+      </c>
+      <c r="DX22" s="2">
+        <f t="shared" si="71"/>
+        <v>2291.53796456189</v>
+      </c>
+      <c r="DY22" s="2">
+        <f t="shared" si="71"/>
+        <v>2268.6225849162711</v>
+      </c>
+      <c r="DZ22" s="2">
+        <f t="shared" si="71"/>
+        <v>2245.9363590671082</v>
+      </c>
+      <c r="EA22" s="2">
+        <f t="shared" si="71"/>
+        <v>2223.476995476437</v>
+      </c>
+      <c r="EB22" s="2">
+        <f t="shared" si="71"/>
+        <v>2201.2422255216725</v>
+      </c>
+      <c r="EC22" s="2">
+        <f t="shared" si="71"/>
+        <v>2179.2298032664557</v>
+      </c>
+      <c r="ED22" s="2">
+        <f t="shared" si="71"/>
+        <v>2157.4375052337909</v>
+      </c>
+      <c r="EE22" s="2">
+        <f t="shared" si="71"/>
+        <v>2135.863130181453</v>
+      </c>
+    </row>
+    <row r="23" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>2</v>
       </c>
@@ -1245,289 +2664,825 @@
       <c r="J23" s="6">
         <v>790</v>
       </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K23" s="6">
+        <v>790</v>
+      </c>
+      <c r="L23" s="6">
+        <v>790</v>
+      </c>
+      <c r="M23" s="6">
+        <v>790</v>
+      </c>
+      <c r="N23" s="6">
+        <v>790</v>
+      </c>
+      <c r="O23" s="6">
+        <v>790</v>
+      </c>
+      <c r="P23" s="6">
+        <v>790</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>790</v>
+      </c>
+      <c r="R23" s="6">
+        <v>790</v>
+      </c>
+      <c r="S23" s="6">
+        <v>790</v>
+      </c>
+      <c r="T23" s="6">
+        <v>790</v>
+      </c>
+      <c r="U23" s="6">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="24" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E24" s="7">
-        <f>E22/E23</f>
+        <f t="shared" ref="E24:K24" si="72">E22/E23</f>
         <v>-1.7240506329113925</v>
       </c>
       <c r="F24" s="7">
-        <f>F22/F23</f>
+        <f t="shared" si="72"/>
         <v>-1.4341772151898735</v>
       </c>
       <c r="G24" s="7">
-        <f>G22/G23</f>
+        <f t="shared" si="72"/>
         <v>5.3329113924050633</v>
       </c>
       <c r="H24" s="7">
-        <f>H22/H23</f>
+        <f t="shared" si="72"/>
         <v>5.3759493670886078</v>
       </c>
       <c r="I24" s="7">
-        <f>I22/I23</f>
+        <f t="shared" si="72"/>
         <v>4.7962025316455694</v>
       </c>
       <c r="J24" s="7">
-        <f>J22/J23</f>
+        <f t="shared" si="72"/>
         <v>5.3569620253164558</v>
       </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K24" s="7">
+        <f t="shared" si="72"/>
+        <v>6.6315285063291123</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" ref="L24" si="73">L22/L23</f>
+        <v>6.8561499058227851</v>
+      </c>
+      <c r="M24" s="7">
+        <f t="shared" ref="M24" si="74">M22/M23</f>
+        <v>7.0236969019139242</v>
+      </c>
+      <c r="N24" s="7">
+        <f t="shared" ref="N24" si="75">N22/N23</f>
+        <v>7.1948990779066344</v>
+      </c>
+      <c r="O24" s="7">
+        <f t="shared" ref="O24" si="76">O22/O23</f>
+        <v>7.3698325797987403</v>
+      </c>
+      <c r="P24" s="7">
+        <f t="shared" ref="P24" si="77">P22/P23</f>
+        <v>7.5485751069320308</v>
+      </c>
+      <c r="Q24" s="7">
+        <f t="shared" ref="Q24" si="78">Q22/Q23</f>
+        <v>7.7312059433633582</v>
+      </c>
+      <c r="R24" s="7">
+        <f t="shared" ref="R24" si="79">R22/R23</f>
+        <v>7.917805989866241</v>
+      </c>
+      <c r="S24" s="7">
+        <f t="shared" ref="S24" si="80">S22/S23</f>
+        <v>8.1084577965755376</v>
+      </c>
+      <c r="T24" s="7">
+        <f t="shared" ref="T24" si="81">T22/T23</f>
+        <v>8.3032455962881375</v>
+      </c>
+      <c r="U24" s="7">
+        <f t="shared" ref="U24" si="82">U22/U23</f>
+        <v>8.5022553384327999</v>
+      </c>
+    </row>
+    <row r="26" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="9">
-        <f t="shared" ref="E26:J26" si="0">F3/E3-1</f>
+        <f t="shared" ref="F26:I26" si="83">F3/E3-1</f>
         <v>-0.29180737251340849</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="83"/>
         <v>4.4818881230966445E-2</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="83"/>
         <v>0.12682889413028064</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="83"/>
         <v>0.11372802613889688</v>
       </c>
       <c r="J26" s="9">
         <f>J3/I3-1</f>
         <v>5.7818659658344318E-2</v>
       </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K26" s="9">
+        <f t="shared" ref="K26:U26" si="84">K3/J3-1</f>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="L26" s="9">
+        <f t="shared" si="84"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="M26" s="9">
+        <f t="shared" si="84"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="N26" s="9">
+        <f t="shared" si="84"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="O26" s="9">
+        <f t="shared" si="84"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="P26" s="9">
+        <f t="shared" si="84"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="Q26" s="9">
+        <f t="shared" si="84"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="R26" s="9">
+        <f t="shared" si="84"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="S26" s="9">
+        <f t="shared" si="84"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="T26" s="9">
+        <f t="shared" si="84"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="U26" s="9">
+        <f t="shared" si="84"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" ref="E27:J27" si="1">E5/E3</f>
+        <f t="shared" ref="E27:I27" si="85">E5/E3</f>
         <v>0.14905360538040238</v>
       </c>
       <c r="F27" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="85"/>
         <v>0.11343965379067159</v>
       </c>
       <c r="G27" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="85"/>
         <v>0.18468235248998063</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="85"/>
         <v>0.17989210898014057</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="85"/>
         <v>0.15347003636585888</v>
       </c>
       <c r="J27" s="9">
         <f>J5/J3</f>
         <v>0.15419615773508594</v>
       </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="9">
+        <f t="shared" ref="K27:U27" si="86">K5/K3</f>
+        <v>0.17</v>
+      </c>
+      <c r="L27" s="9">
+        <f t="shared" si="86"/>
+        <v>0.17</v>
+      </c>
+      <c r="M27" s="9">
+        <f t="shared" si="86"/>
+        <v>0.17</v>
+      </c>
+      <c r="N27" s="9">
+        <f t="shared" si="86"/>
+        <v>0.17</v>
+      </c>
+      <c r="O27" s="9">
+        <f t="shared" si="86"/>
+        <v>0.17</v>
+      </c>
+      <c r="P27" s="9">
+        <f t="shared" si="86"/>
+        <v>0.17</v>
+      </c>
+      <c r="Q27" s="9">
+        <f t="shared" si="86"/>
+        <v>0.17</v>
+      </c>
+      <c r="R27" s="9">
+        <f t="shared" si="86"/>
+        <v>0.17</v>
+      </c>
+      <c r="S27" s="9">
+        <f t="shared" si="86"/>
+        <v>0.17</v>
+      </c>
+      <c r="T27" s="9">
+        <f t="shared" si="86"/>
+        <v>0.17</v>
+      </c>
+      <c r="U27" s="9">
+        <f t="shared" si="86"/>
+        <v>0.17</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y27" s="9">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="28" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E28" s="9">
-        <f t="shared" ref="E28:J28" si="2">E6/E3</f>
+        <f t="shared" ref="E28:I28" si="87">E6/E3</f>
         <v>1.2883452992423168E-2</v>
       </c>
       <c r="F28" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="87"/>
         <v>1.4365282897900305E-2</v>
       </c>
       <c r="G28" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="87"/>
         <v>1.3672361886133962E-2</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="87"/>
         <v>1.3409798682844648E-2</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="87"/>
         <v>1.3247562876264401E-2</v>
       </c>
       <c r="J28" s="9">
         <f>J6/J3</f>
         <v>1.2667918532428138E-2</v>
       </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K28" s="9">
+        <f t="shared" ref="K28:U28" si="88">K6/K3</f>
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="L28" s="9">
+        <f t="shared" si="88"/>
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="M28" s="9">
+        <f t="shared" si="88"/>
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="N28" s="9">
+        <f t="shared" si="88"/>
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="O28" s="9">
+        <f t="shared" si="88"/>
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="P28" s="9">
+        <f t="shared" si="88"/>
+        <v>1.3000000000000001E-2</v>
+      </c>
+      <c r="Q28" s="9">
+        <f t="shared" si="88"/>
+        <v>1.3000000000000001E-2</v>
+      </c>
+      <c r="R28" s="9">
+        <f t="shared" si="88"/>
+        <v>1.2999999999999998E-2</v>
+      </c>
+      <c r="S28" s="9">
+        <f t="shared" si="88"/>
+        <v>1.3000000000000001E-2</v>
+      </c>
+      <c r="T28" s="9">
+        <f t="shared" si="88"/>
+        <v>1.3000000000000001E-2</v>
+      </c>
+      <c r="U28" s="9">
+        <f t="shared" si="88"/>
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y28" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>36</v>
       </c>
       <c r="E29" s="9"/>
       <c r="F29" s="9">
-        <f t="shared" ref="E29:J29" si="3">F7/E7-1</f>
+        <f t="shared" ref="F29:I29" si="89">F7/E7-1</f>
         <v>-0.72723787617404634</v>
       </c>
       <c r="G29" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="89"/>
         <v>-5.9030217849613487E-2</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="89"/>
         <v>8.4391336818521179E-2</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="89"/>
         <v>0.1391184573002755</v>
       </c>
       <c r="J29" s="9">
         <f>J7/I7-1</f>
         <v>5.4413542926239344E-2</v>
       </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K29" s="9">
+        <f t="shared" ref="K29:U29" si="90">K7/J7-1</f>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="L29" s="9">
+        <f t="shared" si="90"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="M29" s="9">
+        <f t="shared" si="90"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="N29" s="9">
+        <f t="shared" si="90"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="O29" s="9">
+        <f t="shared" si="90"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="P29" s="9">
+        <f t="shared" si="90"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="Q29" s="9">
+        <f t="shared" si="90"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="R29" s="9">
+        <f t="shared" si="90"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="S29" s="9">
+        <f t="shared" si="90"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="T29" s="9">
+        <f t="shared" si="90"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="U29" s="9">
+        <f t="shared" si="90"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y29" s="6">
+        <f>NPV(Y28,K22:EE22)</f>
+        <v>83555.627301093453</v>
+      </c>
+    </row>
+    <row r="30" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="9">
-        <f t="shared" ref="E30:J30" si="4">F8/E8-1</f>
+        <f t="shared" ref="F30:I30" si="91">F8/E8-1</f>
         <v>-0.14889815366289461</v>
       </c>
       <c r="G30" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="91"/>
         <v>-3.9188243526941946E-2</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="91"/>
         <v>0.12126729788783686</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="91"/>
         <v>5.7810977590126766E-2</v>
       </c>
       <c r="J30" s="9">
         <f>J8/I8-1</f>
         <v>-2.149217070924192E-3</v>
       </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K30" s="9">
+        <f t="shared" ref="K30:U30" si="92">K8/J8-1</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="L30" s="9">
+        <f t="shared" si="92"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="M30" s="9">
+        <f t="shared" si="92"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="N30" s="9">
+        <f t="shared" si="92"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="O30" s="9">
+        <f t="shared" si="92"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="P30" s="9">
+        <f t="shared" si="92"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="Q30" s="9">
+        <f t="shared" si="92"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="R30" s="9">
+        <f t="shared" si="92"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="S30" s="9">
+        <f t="shared" si="92"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="T30" s="9">
+        <f t="shared" si="92"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="U30" s="9">
+        <f t="shared" si="92"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="X30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y30" s="6">
+        <f>Main!D8</f>
+        <v>724</v>
+      </c>
+    </row>
+    <row r="31" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" ref="E31:J31" si="5">E10/E3</f>
+        <f t="shared" ref="E31:I31" si="93">E10/E3</f>
         <v>1.4500979028916824E-2</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="93"/>
         <v>1.3303414008655234E-2</v>
       </c>
       <c r="G31" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="93"/>
         <v>9.2676753149628949E-2</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="93"/>
         <v>8.9375967870939196E-2</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="93"/>
         <v>6.5183510069370162E-2</v>
       </c>
       <c r="J31" s="9">
         <f>J10/J3</f>
         <v>6.9391882132023686E-2</v>
       </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K31" s="9">
+        <f t="shared" ref="K31:U31" si="94">K10/K3</f>
+        <v>8.53150368337426E-2</v>
+      </c>
+      <c r="L31" s="9">
+        <f t="shared" si="94"/>
+        <v>8.576643073811932E-2</v>
+      </c>
+      <c r="M31" s="9">
+        <f t="shared" si="94"/>
+        <v>8.6217824642496027E-2</v>
+      </c>
+      <c r="N31" s="9">
+        <f t="shared" si="94"/>
+        <v>8.6664793116437683E-2</v>
+      </c>
+      <c r="O31" s="9">
+        <f t="shared" si="94"/>
+        <v>8.710737954651715E-2</v>
+      </c>
+      <c r="P31" s="9">
+        <f t="shared" si="94"/>
+        <v>8.7545626893948805E-2</v>
+      </c>
+      <c r="Q31" s="9">
+        <f t="shared" si="94"/>
+        <v>8.7979577698758554E-2</v>
+      </c>
+      <c r="R31" s="9">
+        <f t="shared" si="94"/>
+        <v>8.8409274083913317E-2</v>
+      </c>
+      <c r="S31" s="9">
+        <f t="shared" si="94"/>
+        <v>8.8834757759409716E-2</v>
+      </c>
+      <c r="T31" s="9">
+        <f t="shared" si="94"/>
+        <v>8.9256070026322784E-2</v>
+      </c>
+      <c r="U31" s="9">
+        <f t="shared" si="94"/>
+        <v>8.9673251780815158E-2</v>
+      </c>
+      <c r="X31" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y31" s="6">
+        <f>Y29+Y30</f>
+        <v>84279.627301093453</v>
+      </c>
+    </row>
+    <row r="32" spans="2:135" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="9">
-        <f t="shared" ref="E32:J32" si="6">E20/E19</f>
+        <f t="shared" ref="E32:I32" si="95">E20/E19</f>
         <v>2.2453007518796992</v>
       </c>
       <c r="F32" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="95"/>
         <v>-3.4513274336283185E-2</v>
       </c>
       <c r="G32" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="95"/>
         <v>0.16968370797692461</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="95"/>
         <v>0.18502463054187193</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="95"/>
         <v>0.24239882574963303</v>
       </c>
       <c r="J32" s="9">
         <f>J20/J19</f>
         <v>0.24829493087557603</v>
       </c>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K32" s="9">
+        <f t="shared" ref="K32:U32" si="96">K20/K19</f>
+        <v>0.23</v>
+      </c>
+      <c r="L32" s="9">
+        <f t="shared" si="96"/>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="M32" s="9">
+        <f t="shared" si="96"/>
+        <v>0.23</v>
+      </c>
+      <c r="N32" s="9">
+        <f t="shared" si="96"/>
+        <v>0.23</v>
+      </c>
+      <c r="O32" s="9">
+        <f t="shared" si="96"/>
+        <v>0.23</v>
+      </c>
+      <c r="P32" s="9">
+        <f t="shared" si="96"/>
+        <v>0.23</v>
+      </c>
+      <c r="Q32" s="9">
+        <f t="shared" si="96"/>
+        <v>0.23</v>
+      </c>
+      <c r="R32" s="9">
+        <f t="shared" si="96"/>
+        <v>0.23</v>
+      </c>
+      <c r="S32" s="9">
+        <f t="shared" si="96"/>
+        <v>0.23</v>
+      </c>
+      <c r="T32" s="9">
+        <f t="shared" si="96"/>
+        <v>0.23</v>
+      </c>
+      <c r="U32" s="9">
+        <f t="shared" si="96"/>
+        <v>0.23</v>
+      </c>
+      <c r="X32" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y32" s="10">
+        <f>Y31/U23</f>
+        <v>106.68307253302969</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E33" s="9">
-        <f t="shared" ref="E33:J33" si="7">E21/E19</f>
+        <f t="shared" ref="E33:I33" si="97">E21/E19</f>
         <v>3.4774436090225562E-2</v>
       </c>
       <c r="F33" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="97"/>
         <v>3.1858407079646017E-2</v>
       </c>
       <c r="G33" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="97"/>
         <v>-7.7581062263775615E-3</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="97"/>
         <v>-2.187192118226601E-2</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="97"/>
         <v>-3.6905011532816105E-2</v>
       </c>
       <c r="J33" s="9">
         <f>J21/J19</f>
         <v>-2.838709677419355E-2</v>
       </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K33" s="9">
+        <f t="shared" ref="K33:U33" si="98">K21/K19</f>
+        <v>-2.9999999999999995E-2</v>
+      </c>
+      <c r="L33" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.03</v>
+      </c>
+      <c r="M33" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.03</v>
+      </c>
+      <c r="N33" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.03</v>
+      </c>
+      <c r="O33" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.03</v>
+      </c>
+      <c r="P33" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.03</v>
+      </c>
+      <c r="Q33" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.03</v>
+      </c>
+      <c r="R33" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.03</v>
+      </c>
+      <c r="S33" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.03</v>
+      </c>
+      <c r="T33" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.03</v>
+      </c>
+      <c r="U33" s="9">
+        <f t="shared" si="98"/>
+        <v>-0.03</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y33" s="10">
+        <f>Main!D3</f>
+        <v>137.16</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E34" s="9">
-        <f t="shared" ref="E34:J34" si="8">E22/E3</f>
+        <f t="shared" ref="E34:I34" si="99">E22/E3</f>
         <v>-1.9325179488634752E-2</v>
       </c>
       <c r="F34" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="99"/>
         <v>-2.2699951915371053E-2</v>
       </c>
       <c r="G34" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="99"/>
         <v>8.078774281386028E-2</v>
       </c>
       <c r="H34" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="99"/>
         <v>7.2273369297006618E-2</v>
       </c>
       <c r="I34" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="99"/>
         <v>5.7895058521529201E-2</v>
       </c>
       <c r="J34" s="9">
         <f>J22/J3</f>
         <v>6.1129568106312294E-2</v>
       </c>
+      <c r="K34" s="9">
+        <f t="shared" ref="K34:U34" si="100">K22/K3</f>
+        <v>7.2763412926810281E-2</v>
+      </c>
+      <c r="L34" s="9">
+        <f t="shared" si="100"/>
+        <v>7.3036928371480306E-2</v>
+      </c>
+      <c r="M34" s="9">
+        <f t="shared" si="100"/>
+        <v>7.3354673065756312E-2</v>
+      </c>
+      <c r="N34" s="9">
+        <f t="shared" si="100"/>
+        <v>7.3669302615970822E-2</v>
+      </c>
+      <c r="O34" s="9">
+        <f t="shared" si="100"/>
+        <v>7.3980847562751847E-2</v>
+      </c>
+      <c r="P34" s="9">
+        <f t="shared" si="100"/>
+        <v>7.4289338147309536E-2</v>
+      </c>
+      <c r="Q34" s="9">
+        <f t="shared" si="100"/>
+        <v>7.4594804314371543E-2</v>
+      </c>
+      <c r="R34" s="9">
+        <f t="shared" si="100"/>
+        <v>7.4897275715089834E-2</v>
+      </c>
+      <c r="S34" s="9">
+        <f t="shared" si="100"/>
+        <v>7.5196781709918711E-2</v>
+      </c>
+      <c r="T34" s="9">
+        <f t="shared" si="100"/>
+        <v>7.5493351371464942E-2</v>
+      </c>
+      <c r="U34" s="9">
+        <f t="shared" si="100"/>
+        <v>7.5787013487309748E-2</v>
+      </c>
+      <c r="X34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y34" s="11">
+        <f>Y32/Y33-1</f>
+        <v>-0.22219982113568326</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="X35" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y35" s="12" t="s">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Financial Analysis/AIR.xlsx
+++ b/Financial Analysis/AIR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA9C257-278C-4FD2-ADC8-BDE283AACCAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E9D055-3D69-4B3B-8300-07C9CBC5FA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{07D530EB-ED3E-4FE7-ACCA-598769C814C3}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="68">
   <si>
     <t>AIR</t>
   </si>
@@ -220,18 +220,28 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
+  </si>
+  <si>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00\ [$€-484]"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ [$€-1]"/>
+    <numFmt numFmtId="166" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,6 +274,15 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -310,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -330,6 +349,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -776,14 +797,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>183.84</v>
+        <v>203.55</v>
       </c>
       <c r="E3" s="5">
-        <v>45906</v>
+        <v>45934</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45906</v>
+        <v>45934</v>
       </c>
       <c r="G3" s="5">
         <v>45959</v>
@@ -807,7 +828,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>145104.91199999998</v>
+        <v>160662.01500000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -849,7 +870,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>130841.91199999998</v>
+        <v>146399.01500000001</v>
       </c>
     </row>
   </sheetData>
@@ -859,7 +880,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE816CCF-DE88-4637-A6DE-75C4B7BD6D1F}">
-  <dimension ref="B2:EU35"/>
+  <dimension ref="B2:EU41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -3688,47 +3709,47 @@
         <v>790</v>
       </c>
       <c r="AA23" s="6">
-        <f>789.3</f>
+        <f t="shared" ref="AA23:AK23" si="125">789.3</f>
         <v>789.3</v>
       </c>
       <c r="AB23" s="6">
-        <f>789.3</f>
+        <f t="shared" si="125"/>
         <v>789.3</v>
       </c>
       <c r="AC23" s="6">
-        <f>789.3</f>
+        <f t="shared" si="125"/>
         <v>789.3</v>
       </c>
       <c r="AD23" s="6">
-        <f>789.3</f>
+        <f t="shared" si="125"/>
         <v>789.3</v>
       </c>
       <c r="AE23" s="6">
-        <f>789.3</f>
+        <f t="shared" si="125"/>
         <v>789.3</v>
       </c>
       <c r="AF23" s="6">
-        <f>789.3</f>
+        <f t="shared" si="125"/>
         <v>789.3</v>
       </c>
       <c r="AG23" s="6">
-        <f>789.3</f>
+        <f t="shared" si="125"/>
         <v>789.3</v>
       </c>
       <c r="AH23" s="6">
-        <f>789.3</f>
+        <f t="shared" si="125"/>
         <v>789.3</v>
       </c>
       <c r="AI23" s="6">
-        <f>789.3</f>
+        <f t="shared" si="125"/>
         <v>789.3</v>
       </c>
       <c r="AJ23" s="6">
-        <f>789.3</f>
+        <f t="shared" si="125"/>
         <v>789.3</v>
       </c>
       <c r="AK23" s="6">
-        <f>789.3</f>
+        <f t="shared" si="125"/>
         <v>789.3</v>
       </c>
     </row>
@@ -3737,119 +3758,119 @@
         <v>31</v>
       </c>
       <c r="G24" s="7">
-        <f t="shared" ref="G24" si="125">G22/G23</f>
+        <f t="shared" ref="G24" si="126">G22/G23</f>
         <v>0.58987341772151902</v>
       </c>
       <c r="H24" s="7">
-        <f t="shared" ref="H24" si="126">H22/H23</f>
+        <f t="shared" ref="H24" si="127">H22/H23</f>
         <v>1.3417721518987342</v>
       </c>
       <c r="I24" s="7">
-        <f t="shared" ref="I24:J24" si="127">I22/I23</f>
+        <f t="shared" ref="I24:J24" si="128">I22/I23</f>
         <v>1.0202531645569621</v>
       </c>
       <c r="J24" s="7">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>1.8443037974683545</v>
       </c>
       <c r="K24" s="7">
-        <f t="shared" ref="K24:L24" si="128">K22/K23</f>
+        <f t="shared" ref="K24:L24" si="129">K22/K23</f>
         <v>0.75316455696202533</v>
       </c>
       <c r="L24" s="7">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.29113924050632911</v>
       </c>
       <c r="M24" s="7">
-        <f t="shared" ref="M24:O24" si="129">M22/M23</f>
+        <f t="shared" ref="M24:O24" si="130">M22/M23</f>
         <v>1.2443037974683544</v>
       </c>
       <c r="N24" s="7">
-        <f t="shared" ref="N24" si="130">N22/N23</f>
+        <f t="shared" ref="N24" si="131">N22/N23</f>
         <v>3.0683544303797468</v>
       </c>
       <c r="O24" s="7">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>1.0037974683544304</v>
       </c>
       <c r="P24" s="7">
-        <f t="shared" ref="P24:R24" si="131">P22/P23</f>
+        <f t="shared" ref="P24:R24" si="132">P22/P23</f>
         <v>0.92740402888635509</v>
       </c>
       <c r="Q24" s="7">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>1.1914027629545165</v>
       </c>
       <c r="R24" s="7">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>3.069715869758014</v>
       </c>
       <c r="U24" s="7">
-        <f t="shared" ref="U24:AA24" si="132">U22/U23</f>
+        <f t="shared" ref="U24:AA24" si="133">U22/U23</f>
         <v>-1.7240506329113925</v>
       </c>
       <c r="V24" s="7">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>-1.4341772151898735</v>
       </c>
       <c r="W24" s="7">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>5.3329113924050633</v>
       </c>
       <c r="X24" s="7">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>5.3759493670886078</v>
       </c>
       <c r="Y24" s="7">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>4.7962025316455694</v>
       </c>
       <c r="Z24" s="7">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>5.3569620253164558</v>
       </c>
       <c r="AA24" s="7">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>6.6772182146205497</v>
       </c>
       <c r="AB24" s="7">
-        <f t="shared" ref="AB24" si="133">AB22/AB23</f>
+        <f t="shared" ref="AB24" si="134">AB22/AB23</f>
         <v>7.2973121270999632</v>
       </c>
       <c r="AC24" s="7">
-        <f t="shared" ref="AC24" si="134">AC22/AC23</f>
+        <f t="shared" ref="AC24" si="135">AC22/AC23</f>
         <v>8.2542346713168655</v>
       </c>
       <c r="AD24" s="7">
-        <f t="shared" ref="AD24" si="135">AD22/AD23</f>
+        <f t="shared" ref="AD24" si="136">AD22/AD23</f>
         <v>8.4486947723803496</v>
       </c>
       <c r="AE24" s="7">
-        <f t="shared" ref="AE24" si="136">AE22/AE23</f>
+        <f t="shared" ref="AE24" si="137">AE22/AE23</f>
         <v>8.647337829541474</v>
       </c>
       <c r="AF24" s="7">
-        <f t="shared" ref="AF24" si="137">AF22/AF23</f>
+        <f t="shared" ref="AF24" si="138">AF22/AF23</f>
         <v>8.8502504394629558</v>
       </c>
       <c r="AG24" s="7">
-        <f t="shared" ref="AG24" si="138">AG22/AG23</f>
+        <f t="shared" ref="AG24" si="139">AG22/AG23</f>
         <v>9.0575209601161752</v>
       </c>
       <c r="AH24" s="7">
-        <f t="shared" ref="AH24" si="139">AH22/AH23</f>
+        <f t="shared" ref="AH24" si="140">AH22/AH23</f>
         <v>9.269239546301101</v>
       </c>
       <c r="AI24" s="7">
-        <f t="shared" ref="AI24" si="140">AI22/AI23</f>
+        <f t="shared" ref="AI24" si="141">AI22/AI23</f>
         <v>9.4854981858795462</v>
       </c>
       <c r="AJ24" s="7">
-        <f t="shared" ref="AJ24" si="141">AJ22/AJ23</f>
+        <f t="shared" ref="AJ24" si="142">AJ22/AJ23</f>
         <v>9.7063907367360862</v>
       </c>
       <c r="AK24" s="7">
-        <f t="shared" ref="AK24" si="142">AK22/AK23</f>
+        <f t="shared" ref="AK24" si="143">AK22/AK23</f>
         <v>9.9320129644811477</v>
       </c>
     </row>
@@ -3882,32 +3903,32 @@
         <v>5.549493374902581E-2</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" ref="P26:R26" si="143">P3/L3-1</f>
+        <f t="shared" ref="P26:R26" si="144">P3/L3-1</f>
         <v>4.5639262269459024E-3</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="U26" s="9"/>
       <c r="V26" s="9">
-        <f t="shared" ref="V26:Y26" si="144">V3/U3-1</f>
+        <f t="shared" ref="V26:Y26" si="145">V3/U3-1</f>
         <v>-0.29180737251340849</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>4.4818881230966445E-2</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0.12682889413028064</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0.11372802613889688</v>
       </c>
       <c r="Z26" s="9">
@@ -3915,47 +3936,47 @@
         <v>5.7818659658344318E-2</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" ref="AA26:AK26" si="145">AA3/Z3-1</f>
+        <f t="shared" ref="AA26:AK26" si="146">AA3/Z3-1</f>
         <v>6.063758486205395E-2</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC26" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK26" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -3964,71 +3985,71 @@
         <v>34</v>
       </c>
       <c r="G27" s="9">
-        <f t="shared" ref="G27" si="146">G5/G3</f>
+        <f t="shared" ref="G27" si="147">G5/G3</f>
         <v>0.14112046246705773</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" ref="H27:I27" si="147">H5/H3</f>
+        <f t="shared" ref="H27:I27" si="148">H5/H3</f>
         <v>0.17968553459119496</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>0.13767872726052224</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" ref="J27" si="148">J5/J3</f>
+        <f t="shared" ref="J27" si="149">J5/J3</f>
         <v>0.1518832474001573</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" ref="K27:L27" si="149">K5/K3</f>
+        <f t="shared" ref="K27:L27" si="150">K5/K3</f>
         <v>0.15066250974279033</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.14004376367614879</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" ref="M27:O27" si="150">M5/M3</f>
+        <f t="shared" ref="M27:O27" si="151">M5/M3</f>
         <v>0.1572439288673593</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" ref="N27" si="151">N5/N3</f>
+        <f t="shared" ref="N27" si="152">N5/N3</f>
         <v>0.16325457193720666</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>0.1386796632698272</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" ref="P27:R27" si="152">P5/P3</f>
+        <f t="shared" ref="P27:R27" si="153">P5/P3</f>
         <v>0.14762260393328355</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>0.15</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>0.17</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" ref="U27:Y27" si="153">U5/U3</f>
+        <f t="shared" ref="U27:Y27" si="154">U5/U3</f>
         <v>0.14905360538040238</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>0.11343965379067159</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>0.18468235248998063</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>0.17989210898014057</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>0.15347003636585888</v>
       </c>
       <c r="Z27" s="9">
@@ -4036,47 +4057,47 @@
         <v>0.15419615773508594</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" ref="AA27:AK27" si="154">AA5/AA3</f>
+        <f t="shared" ref="AA27:AK27" si="155">AA5/AA3</f>
         <v>0.16</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>0.17</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>0.18</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>0.18</v>
       </c>
       <c r="AE27" s="9">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>0.18</v>
       </c>
       <c r="AF27" s="9">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>0.18</v>
       </c>
       <c r="AG27" s="9">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>0.18</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>0.18</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>0.18</v>
       </c>
       <c r="AJ27" s="9">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>0.18</v>
       </c>
       <c r="AK27" s="9">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>0.18</v>
       </c>
       <c r="AN27" s="1" t="s">
@@ -4091,71 +4112,71 @@
         <v>35</v>
       </c>
       <c r="G28" s="9">
-        <f t="shared" ref="G28" si="155">G6/G3</f>
+        <f t="shared" ref="G28" si="156">G6/G3</f>
         <v>1.7427526991413755E-2</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" ref="H28:I28" si="156">H6/H3</f>
+        <f t="shared" ref="H28:I28" si="157">H6/H3</f>
         <v>1.3773584905660377E-2</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>1.4633818889709337E-2</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" ref="J28" si="157">J6/J3</f>
+        <f t="shared" ref="J28" si="158">J6/J3</f>
         <v>9.831337935855982E-3</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" ref="K28:L28" si="158">K6/K3</f>
+        <f t="shared" ref="K28:L28" si="159">K6/K3</f>
         <v>1.7614964925954792E-2</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>1.4629571741169115E-2</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" ref="M28:O28" si="159">M6/M3</f>
+        <f t="shared" ref="M28:O28" si="160">M6/M3</f>
         <v>1.2939001848428836E-2</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" ref="N28" si="160">N6/N3</f>
+        <f t="shared" ref="N28" si="161">N6/N3</f>
         <v>8.6583589577601556E-3</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>1.6171909614532565E-2</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" ref="P28:R28" si="161">P6/P3</f>
+        <f t="shared" ref="P28:R28" si="162">P6/P3</f>
         <v>1.300721931789893E-2</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" ref="U28:Y28" si="162">U6/U3</f>
+        <f t="shared" ref="U28:Y28" si="163">U6/U3</f>
         <v>1.2883452992423168E-2</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>1.4365282897900305E-2</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>1.3672361886133962E-2</v>
       </c>
       <c r="X28" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>1.3409798682844648E-2</v>
       </c>
       <c r="Y28" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>1.3247562876264401E-2</v>
       </c>
       <c r="Z28" s="9">
@@ -4163,47 +4184,47 @@
         <v>1.2667918532428138E-2</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" ref="AA28:AK28" si="163">AA6/AA3</f>
+        <f t="shared" ref="AA28:AK28" si="164">AA6/AA3</f>
         <v>1.2105512152458588E-2</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>1.3000000000000001E-2</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>1.2999999999999998E-2</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>1.3000000000000001E-2</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>1.2999999999999998E-2</v>
       </c>
       <c r="AK28" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="AN28" s="1" t="s">
@@ -4222,52 +4243,52 @@
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
       <c r="K29" s="9">
-        <f t="shared" ref="K29:O30" si="164">K7/G7-1</f>
+        <f t="shared" ref="K29:O30" si="165">K7/G7-1</f>
         <v>0.1518324607329844</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>0</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>-1.4814814814814836E-2</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>8.9834515366430168E-2</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>1.3636363636363669E-2</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" ref="P29:R29" si="165">P7/L7-1</f>
+        <f t="shared" ref="P29:R29" si="166">P7/L7-1</f>
         <v>-3.3783783783783772E-2</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="U29" s="9"/>
       <c r="V29" s="9">
-        <f t="shared" ref="V29:Y29" si="166">V7/U7-1</f>
+        <f t="shared" ref="V29:Y29" si="167">V7/U7-1</f>
         <v>-0.72723787617404634</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>-5.9030217849613487E-2</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>8.4391336818521179E-2</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0.1391184573002755</v>
       </c>
       <c r="Z29" s="9">
@@ -4275,47 +4296,47 @@
         <v>5.4413542926239344E-2</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" ref="AA29:AK29" si="167">AA7/Z7-1</f>
+        <f t="shared" ref="AA29:AK29" si="168">AA7/Z7-1</f>
         <v>4.7018348623852901E-3</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK29" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN29" s="1" t="s">
@@ -4335,52 +4356,52 @@
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>8.7847730600292717E-2</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>0.13636363636363646</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>2.9891304347826164E-2</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>-0.17522935779816518</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>-9.4212651413189796E-2</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" ref="P30:R30" si="168">P8/L8-1</f>
+        <f t="shared" ref="P30:R30" si="169">P8/L8-1</f>
         <v>-0.13764705882352946</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>-7.999999999999996E-2</v>
       </c>
       <c r="U30" s="9"/>
       <c r="V30" s="9">
-        <f t="shared" ref="V30:Y30" si="169">V8/U8-1</f>
+        <f t="shared" ref="V30:Y30" si="170">V8/U8-1</f>
         <v>-0.14889815366289461</v>
       </c>
       <c r="W30" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>-3.9188243526941946E-2</v>
       </c>
       <c r="X30" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>0.12126729788783686</v>
       </c>
       <c r="Y30" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>5.7810977590126766E-2</v>
       </c>
       <c r="Z30" s="9">
@@ -4388,47 +4409,47 @@
         <v>-2.149217070924192E-3</v>
       </c>
       <c r="AA30" s="9">
-        <f t="shared" ref="AA30:AK30" si="170">AA8/Z8-1</f>
+        <f t="shared" ref="AA30:AK30" si="171">AA8/Z8-1</f>
         <v>-0.10299076923076933</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK30" s="9">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN30" s="1" t="s">
@@ -4444,71 +4465,71 @@
         <v>38</v>
       </c>
       <c r="G31" s="9">
-        <f t="shared" ref="G31" si="171">G10/G3</f>
+        <f t="shared" ref="G31" si="172">G10/G3</f>
         <v>3.3154807447079826E-2</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" ref="H31:I31" si="172">H10/H3</f>
+        <f t="shared" ref="H31:I31" si="173">H10/H3</f>
         <v>9.0943396226415091E-2</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>4.6452305833389274E-2</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" ref="J31" si="173">J10/J3</f>
+        <f t="shared" ref="J31" si="174">J10/J3</f>
         <v>7.5941623700078648E-2</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" ref="K31:L31" si="174">K10/K3</f>
+        <f t="shared" ref="K31:L31" si="175">K10/K3</f>
         <v>4.0841777084957134E-2</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>4.4513910597061584E-2</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" ref="M31:O31" si="175">M10/M3</f>
+        <f t="shared" ref="M31:O31" si="176">M10/M3</f>
         <v>7.0558990375422265E-2</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" ref="N31" si="176">N10/N3</f>
+        <f t="shared" ref="N31" si="177">N10/N3</f>
         <v>9.9571128014241783E-2</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>3.9875941515285777E-2</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" ref="P31:R31" si="177">P10/P3</f>
+        <f t="shared" ref="P31:R31" si="178">P10/P3</f>
         <v>6.2297734627831718E-2</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>7.1506450258984472E-2</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.11328339390016037</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" ref="U31:Y31" si="178">U10/U3</f>
+        <f t="shared" ref="U31:Y31" si="179">U10/U3</f>
         <v>1.4500979028916824E-2</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>1.3303414008655234E-2</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>9.2676753149628949E-2</v>
       </c>
       <c r="X31" s="9">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>8.9375967870939196E-2</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>6.5183510069370162E-2</v>
       </c>
       <c r="Z31" s="9">
@@ -4516,47 +4537,47 @@
         <v>6.9391882132023686E-2</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" ref="AA31:AK31" si="179">AA10/AA3</f>
+        <f t="shared" ref="AA31:AK31" si="180">AA10/AA3</f>
         <v>8.4329038510408974E-2</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>9.3820012781515999E-2</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0.10420547490016439</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0.1045871579784339</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0.10496509906573998</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0.10533933484826852</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0.10570990165253702</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0.10607683544892053</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0.1064401718551434</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0.10679994613973662</v>
       </c>
       <c r="AK31" s="9">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0.1071561932254613</v>
       </c>
       <c r="AN31" s="1" t="s">
@@ -4572,71 +4593,71 @@
         <v>28</v>
       </c>
       <c r="G32" s="9">
-        <f t="shared" ref="G32" si="180">G20/G19</f>
+        <f t="shared" ref="G32" si="181">G20/G19</f>
         <v>0.18738404452690166</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" ref="H32:I32" si="181">H20/H19</f>
+        <f t="shared" ref="H32:I32" si="182">H20/H19</f>
         <v>0.30068965517241381</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>0.20125786163522014</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" ref="J32" si="182">J20/J19</f>
+        <f t="shared" ref="J32" si="183">J20/J19</f>
         <v>0.23384446878422782</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" ref="K32:L32" si="183">K20/K19</f>
+        <f t="shared" ref="K32:L32" si="184">K20/K19</f>
         <v>0.3412887828162291</v>
       </c>
       <c r="L32" s="9">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>0.64509803921568631</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" ref="M32:O32" si="184">M20/M19</f>
+        <f t="shared" ref="M32:O32" si="185">M20/M19</f>
         <v>0.24959999999999999</v>
       </c>
       <c r="N32" s="9">
-        <f t="shared" ref="N32" si="185">N20/N19</f>
+        <f t="shared" ref="N32" si="186">N20/N19</f>
         <v>0.14856738592147153</v>
       </c>
       <c r="O32" s="9">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>0.31901279707495428</v>
       </c>
       <c r="P32" s="9">
-        <f t="shared" ref="P32:R32" si="186">P20/P19</f>
+        <f t="shared" ref="P32:R32" si="187">P20/P19</f>
         <v>0.30997038499506419</v>
       </c>
       <c r="Q32" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>0.24</v>
       </c>
       <c r="R32" s="9">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>0.24</v>
       </c>
       <c r="U32" s="9">
-        <f t="shared" ref="U32:Y32" si="187">U20/U19</f>
+        <f t="shared" ref="U32:Y32" si="188">U20/U19</f>
         <v>2.2453007518796992</v>
       </c>
       <c r="V32" s="9">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>-3.4513274336283185E-2</v>
       </c>
       <c r="W32" s="9">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0.16968370797692461</v>
       </c>
       <c r="X32" s="9">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0.18502463054187193</v>
       </c>
       <c r="Y32" s="9">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0.24239882574963303</v>
       </c>
       <c r="Z32" s="9">
@@ -4644,47 +4665,47 @@
         <v>0.24829493087557603</v>
       </c>
       <c r="AA32" s="9">
-        <f t="shared" ref="AA32:AK32" si="188">AA20/AA19</f>
+        <f t="shared" ref="AA32:AK32" si="189">AA20/AA19</f>
         <v>0.2496688838864867</v>
       </c>
       <c r="AB32" s="9">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0.23000000000000004</v>
       </c>
       <c r="AC32" s="9">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0.23</v>
       </c>
       <c r="AD32" s="9">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0.23</v>
       </c>
       <c r="AE32" s="9">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0.23</v>
       </c>
       <c r="AF32" s="9">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0.23</v>
       </c>
       <c r="AG32" s="9">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0.23</v>
       </c>
       <c r="AH32" s="9">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0.23</v>
       </c>
       <c r="AI32" s="9">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0.23</v>
       </c>
       <c r="AJ32" s="9">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="AK32" s="9">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0.23</v>
       </c>
       <c r="AN32" s="1" t="s">
@@ -4700,71 +4721,71 @@
         <v>29</v>
       </c>
       <c r="G33" s="9">
-        <f t="shared" ref="G33" si="189">G21/G19</f>
+        <f t="shared" ref="G33" si="190">G21/G19</f>
         <v>-5.1948051948051951E-2</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" ref="H33:I33" si="190">H21/H19</f>
+        <f t="shared" ref="H33:I33" si="191">H21/H19</f>
         <v>-3.1724137931034485E-2</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>-4.6121593291404611E-2</v>
       </c>
       <c r="J33" s="9">
-        <f t="shared" ref="J33" si="191">J21/J19</f>
+        <f t="shared" ref="J33" si="192">J21/J19</f>
         <v>-3.1763417305585982E-2</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" ref="K33:L33" si="192">K21/K19</f>
+        <f t="shared" ref="K33:L33" si="193">K21/K19</f>
         <v>-5.1312649164677801E-2</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>-9.6078431372549025E-2</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" ref="M33:O33" si="193">M21/M19</f>
+        <f t="shared" ref="M33:O33" si="194">M21/M19</f>
         <v>-3.5999999999999997E-2</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" ref="N33" si="194">N21/N19</f>
+        <f t="shared" ref="N33" si="195">N21/N19</f>
         <v>-6.013441811107181E-3</v>
       </c>
       <c r="O33" s="9">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>-4.3875685557586835E-2</v>
       </c>
       <c r="P33" s="9">
-        <f t="shared" ref="P33:R33" si="195">P21/P19</f>
+        <f t="shared" ref="P33:R33" si="196">P21/P19</f>
         <v>-3.257650542941757E-2</v>
       </c>
       <c r="Q33" s="9">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>-4.0879711635876781E-2</v>
       </c>
       <c r="R33" s="9">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>-1.5360473839897011E-2</v>
       </c>
       <c r="U33" s="9">
-        <f t="shared" ref="U33:Y33" si="196">U21/U19</f>
+        <f t="shared" ref="U33:Y33" si="197">U21/U19</f>
         <v>3.4774436090225562E-2</v>
       </c>
       <c r="V33" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>3.1858407079646017E-2</v>
       </c>
       <c r="W33" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>-7.7581062263775615E-3</v>
       </c>
       <c r="X33" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>-2.187192118226601E-2</v>
       </c>
       <c r="Y33" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>-3.6905011532816105E-2</v>
       </c>
       <c r="Z33" s="9">
@@ -4772,47 +4793,47 @@
         <v>-2.838709677419355E-2</v>
       </c>
       <c r="AA33" s="9">
-        <f t="shared" ref="AA33:AK33" si="197">AA21/AA19</f>
+        <f t="shared" ref="AA33:AK33" si="198">AA21/AA19</f>
         <v>-2.6075013973187504E-2</v>
       </c>
       <c r="AB33" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-0.03</v>
       </c>
       <c r="AC33" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-0.03</v>
       </c>
       <c r="AD33" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-0.03</v>
       </c>
       <c r="AE33" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-0.03</v>
       </c>
       <c r="AF33" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-0.03</v>
       </c>
       <c r="AG33" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-0.03</v>
       </c>
       <c r="AH33" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-0.03</v>
       </c>
       <c r="AI33" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-0.03</v>
       </c>
       <c r="AJ33" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-2.9999999999999995E-2</v>
       </c>
       <c r="AK33" s="9">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v>-0.03</v>
       </c>
       <c r="AN33" s="1" t="s">
@@ -4820,7 +4841,7 @@
       </c>
       <c r="AO33" s="10">
         <f>Main!D3</f>
-        <v>183.84</v>
+        <v>203.55</v>
       </c>
     </row>
     <row r="34" spans="2:41" x14ac:dyDescent="0.3">
@@ -4828,71 +4849,71 @@
         <v>39</v>
       </c>
       <c r="G34" s="9">
-        <f t="shared" ref="G34" si="198">G22/G3</f>
+        <f t="shared" ref="G34" si="199">G22/G3</f>
         <v>3.9615744282921021E-2</v>
       </c>
       <c r="H34" s="9">
-        <f t="shared" ref="H34:I34" si="199">H22/H3</f>
+        <f t="shared" ref="H34:I34" si="200">H22/H3</f>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="I34" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v>5.4104853326173055E-2</v>
       </c>
       <c r="J34" s="9">
-        <f t="shared" ref="J34" si="200">J22/J3</f>
+        <f t="shared" ref="J34" si="201">J22/J3</f>
         <v>6.3663374989076288E-2</v>
       </c>
       <c r="K34" s="9">
-        <f t="shared" ref="K34:L34" si="201">K22/K3</f>
+        <f t="shared" ref="K34:L34" si="202">K22/K3</f>
         <v>4.6375681995323458E-2</v>
       </c>
       <c r="L34" s="9">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v>1.437949359174742E-2</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" ref="M34:O34" si="202">M22/M3</f>
+        <f t="shared" ref="M34:O34" si="203">M22/M3</f>
         <v>6.2655363630569186E-2</v>
       </c>
       <c r="N34" s="9">
-        <f t="shared" ref="N34" si="203">N22/N3</f>
+        <f t="shared" ref="N34" si="204">N22/N3</f>
         <v>9.8074122026217833E-2</v>
       </c>
       <c r="O34" s="9">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v>5.8558558558558557E-2</v>
       </c>
       <c r="P34" s="9">
-        <f t="shared" ref="P34:R34" si="204">P22/P3</f>
+        <f t="shared" ref="P34:R34" si="205">P22/P3</f>
         <v>4.5556385362210607E-2</v>
       </c>
       <c r="Q34" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>5.6545699053657347E-2</v>
       </c>
       <c r="R34" s="9">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v>8.9118816519295568E-2</v>
       </c>
       <c r="U34" s="9">
-        <f t="shared" ref="U34:Y34" si="205">U22/U3</f>
+        <f t="shared" ref="U34:Y34" si="206">U22/U3</f>
         <v>-1.9325179488634752E-2</v>
       </c>
       <c r="V34" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>-2.2699951915371053E-2</v>
       </c>
       <c r="W34" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>8.078774281386028E-2</v>
       </c>
       <c r="X34" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>7.2273369297006618E-2</v>
       </c>
       <c r="Y34" s="9">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v>5.7895058521529201E-2</v>
       </c>
       <c r="Z34" s="9">
@@ -4900,47 +4921,47 @@
         <v>6.1129568106312294E-2</v>
       </c>
       <c r="AA34" s="9">
-        <f t="shared" ref="AA34:AK34" si="206">AA22/AA3</f>
+        <f t="shared" ref="AA34:AK34" si="207">AA22/AA3</f>
         <v>7.1775516741992201E-2</v>
       </c>
       <c r="AB34" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>7.6156408792842495E-2</v>
       </c>
       <c r="AC34" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>8.445399026650996E-2</v>
       </c>
       <c r="AD34" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>8.4748654274749299E-2</v>
       </c>
       <c r="AE34" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>8.5040429420162766E-2</v>
       </c>
       <c r="AF34" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>8.5329344024934903E-2</v>
       </c>
       <c r="AG34" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>8.5615426133581862E-2</v>
       </c>
       <c r="AH34" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>8.5898703515673455E-2</v>
       </c>
       <c r="AI34" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>8.6179203668528825E-2</v>
       </c>
       <c r="AJ34" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>8.6456953819885621E-2</v>
       </c>
       <c r="AK34" s="9">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v>8.6731980930542851E-2</v>
       </c>
       <c r="AN34" s="2" t="s">
@@ -4948,7 +4969,7 @@
       </c>
       <c r="AO34" s="11">
         <f>AO32/AO33-1</f>
-        <v>-0.2375809557708306</v>
+        <v>-0.31140694133583646</v>
       </c>
     </row>
     <row r="35" spans="2:41" x14ac:dyDescent="0.3">
@@ -4956,7 +4977,33 @@
         <v>48</v>
       </c>
       <c r="AO35" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="2:41" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="13" t="s">
         <v>64</v>
+      </c>
+      <c r="P38" s="13">
+        <v>129040</v>
+      </c>
+    </row>
+    <row r="40" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P40" s="14">
+        <f>Main!D9/Model!P38</f>
+        <v>1.1345242947923126</v>
+      </c>
+    </row>
+    <row r="41" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P41" s="9">
+        <f>P38/Main!D9-1</f>
+        <v>-0.11857330460864102</v>
       </c>
     </row>
   </sheetData>
